--- a/data/raw/pob_anual.xlsx
+++ b/data/raw/pob_anual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://6f33fa7f78ea46e2aaca-my.sharepoint.com/personal/marianne_pena_ucr_ac_cr/Documents/cuenta personal/ucr pers/practica profesional/practica dengue/dengue-model/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="11_F25DC773A252ABDACC104827C19B4C825ADE58E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C7E33E9-273B-498D-B407-57DABB968748}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="11_F25DC773A252ABDACC104827C19B4C825ADE58E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27D87B45-17B4-4D3A-8778-191323061B20}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -376,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -388,9 +388,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -406,6 +403,905 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-MX"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>anual!$C$1:$J$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2026</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>anual!$C$2:$J$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>5020970.0892126299</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5051379.2310498413</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5077666.8598168911</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5104906.8366506081</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5135911.6221289076</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5164859.9393230798</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5191823.0799561189</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5217294.9784566956</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9CA9-4920-8535-35ABBDB0681E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="356515408"/>
+        <c:axId val="356503888"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="356515408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="356503888"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="356503888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="356515408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>168275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB136DEE-1E6B-C848-EC17-F0D3CDF62752}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -707,2770 +1603,2771 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2">
+        <f>SUM(C3:C86)</f>
+        <v>5020970.0892126299</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ref="D2:J2" si="0">SUM(D3:D86)</f>
+        <v>5051379.2310498413</v>
+      </c>
+      <c r="E2">
+        <f t="shared" si="0"/>
+        <v>5077666.8598168911</v>
+      </c>
+      <c r="F2">
+        <f t="shared" si="0"/>
+        <v>5104906.8366506081</v>
+      </c>
+      <c r="G2">
+        <f t="shared" si="0"/>
+        <v>5135911.6221289076</v>
+      </c>
+      <c r="H2">
+        <f t="shared" si="0"/>
+        <v>5164859.9393230798</v>
+      </c>
+      <c r="I2">
+        <f t="shared" si="0"/>
+        <v>5191823.0799561189</v>
+      </c>
+      <c r="J2">
+        <f t="shared" si="0"/>
+        <v>5217294.9784566956</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="2">
         <v>101</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C3" s="2">
         <v>347692.45856501424</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>348650.26776199462</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>349339.04667269776</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <v>350104.59507527098</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>351263.9721048784</v>
       </c>
-      <c r="H2">
+      <c r="H3">
         <v>352298.48491473496</v>
       </c>
-      <c r="I2">
+      <c r="I3">
         <v>353209.46325169969</v>
       </c>
-      <c r="J2">
+      <c r="J3">
         <v>354025.91533710225</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L3" t="s">
         <v>92</v>
       </c>
-      <c r="M2">
+      <c r="M3">
         <f>(2019-1900)*12 + 6</f>
         <v>1434</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="2">
+    <row r="4" spans="1:13">
+      <c r="A4" s="2">
         <v>102</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C4" s="2">
         <v>69342.771863127593</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>69663.114948175615</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>69932.998700149314</v>
       </c>
-      <c r="F3">
+      <c r="F4">
         <v>70222.770585836843</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>70578.009000896476</v>
       </c>
-      <c r="H3">
+      <c r="H4">
         <v>70903.348646243947</v>
       </c>
-      <c r="I3">
+      <c r="I4">
         <v>71200.542216543472</v>
       </c>
-      <c r="J3">
+      <c r="J4">
         <v>71474.761565909546</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L4" t="s">
         <v>91</v>
       </c>
-      <c r="M3">
+      <c r="M4">
         <f>(2026-1900)*12 + 6</f>
         <v>1518</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="2">
-        <v>103</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>238762.28232309327</v>
-      </c>
-      <c r="D4">
-        <v>239941.16013864966</v>
-      </c>
-      <c r="E4">
-        <v>240923.14706299681</v>
-      </c>
-      <c r="F4">
-        <v>241942.39958240004</v>
-      </c>
-      <c r="G4">
-        <v>243115.78926006326</v>
-      </c>
-      <c r="H4">
-        <v>244173.39648955272</v>
-      </c>
-      <c r="I4">
-        <v>245126.15066931135</v>
-      </c>
-      <c r="J4">
-        <v>245996.11040902205</v>
-      </c>
-      <c r="L4" t="s">
-        <v>88</v>
-      </c>
-      <c r="M4">
-        <f>(M3-M2)/12</f>
-        <v>7</v>
-      </c>
-    </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2">
-        <v>38240.587050800503</v>
+        <v>238762.28232309327</v>
       </c>
       <c r="D5">
-        <v>38421.960299402584</v>
+        <v>239941.16013864966</v>
       </c>
       <c r="E5">
-        <v>38568.634173293307</v>
+        <v>240923.14706299681</v>
       </c>
       <c r="F5">
-        <v>38715.677630372593</v>
+        <v>241942.39958240004</v>
       </c>
       <c r="G5">
-        <v>38901.008901812573</v>
+        <v>243115.78926006326</v>
       </c>
       <c r="H5">
-        <v>39069.282619475838</v>
+        <v>244173.39648955272</v>
       </c>
       <c r="I5">
-        <v>39220.055612267999</v>
+        <v>245126.15066931135</v>
       </c>
       <c r="J5">
-        <v>39356.469591736779</v>
+        <v>245996.11040902205</v>
       </c>
       <c r="L5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M5">
-        <f>D2</f>
-        <v>348650.26776199462</v>
+        <f>(M4-M3)/12</f>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2">
-        <v>17842.632764587546</v>
+        <v>38240.587050800503</v>
       </c>
       <c r="D6">
-        <v>17878.272285328087</v>
+        <v>38421.960299402584</v>
       </c>
       <c r="E6">
-        <v>17897.748320028411</v>
+        <v>38568.634173293307</v>
       </c>
       <c r="F6">
-        <v>17923.38413421424</v>
+        <v>38715.677630372593</v>
       </c>
       <c r="G6">
-        <v>17960.588407250198</v>
+        <v>38901.008901812573</v>
       </c>
       <c r="H6">
-        <v>17990.175683094181</v>
+        <v>39069.282619475838</v>
       </c>
       <c r="I6">
-        <v>18013.482305817812</v>
+        <v>39220.055612267999</v>
       </c>
       <c r="J6">
-        <v>18032.365445277799</v>
+        <v>39356.469591736779</v>
       </c>
       <c r="L6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M6">
-        <f>((I2-D2)/M4)/D2</f>
-        <v>1.868100218500498E-3</v>
+        <f>D3</f>
+        <v>348650.26776199462</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2">
-        <v>61640.79175785082</v>
+        <v>17842.632764587546</v>
       </c>
       <c r="D7">
-        <v>61883.568498730587</v>
+        <v>17878.272285328087</v>
       </c>
       <c r="E7">
-        <v>62072.626309008207</v>
+        <v>17897.748320028411</v>
       </c>
       <c r="F7">
-        <v>62267.764483050909</v>
+        <v>17923.38413421424</v>
       </c>
       <c r="G7">
-        <v>62493.158179910475</v>
+        <v>17960.588407250198</v>
       </c>
       <c r="H7">
-        <v>62687.94861109223</v>
+        <v>17990.175683094181</v>
       </c>
       <c r="I7">
-        <v>62855.088364956522</v>
+        <v>18013.482305817812</v>
       </c>
       <c r="J7">
-        <v>63000.9997631515</v>
+        <v>18032.365445277799</v>
+      </c>
+      <c r="L7" t="s">
+        <v>90</v>
+      </c>
+      <c r="M7">
+        <f>((I3-D3)/M5)/D3</f>
+        <v>1.868100218500498E-3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2">
-        <v>28301.543605497558</v>
+        <v>61640.79175785082</v>
       </c>
       <c r="D8">
-        <v>28393.757699522528</v>
+        <v>61883.568498730587</v>
       </c>
       <c r="E8">
-        <v>28464.244506693845</v>
+        <v>62072.626309008207</v>
       </c>
       <c r="F8">
-        <v>28542.910569431908</v>
+        <v>62267.764483050909</v>
       </c>
       <c r="G8">
-        <v>28643.998829167758</v>
+        <v>62493.158179910475</v>
       </c>
       <c r="H8">
-        <v>28730.995251532746</v>
+        <v>62687.94861109223</v>
       </c>
       <c r="I8">
-        <v>28803.961020641738</v>
+        <v>62855.088364956522</v>
       </c>
       <c r="J8">
-        <v>28864.910083762261</v>
+        <v>63000.9997631515</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2">
-        <v>137108.97722321076</v>
+        <v>28301.543605497558</v>
       </c>
       <c r="D9">
-        <v>137672.80834832694</v>
+        <v>28393.757699522528</v>
       </c>
       <c r="E9">
-        <v>138122.72983772951</v>
+        <v>28464.244506693845</v>
       </c>
       <c r="F9">
-        <v>138587.59880102781</v>
+        <v>28542.910569431908</v>
       </c>
       <c r="G9">
-        <v>139178.941327529</v>
+        <v>28643.998829167758</v>
       </c>
       <c r="H9">
-        <v>139708.29743037571</v>
+        <v>28730.995251532746</v>
       </c>
       <c r="I9">
-        <v>140178.35169281636</v>
+        <v>28803.961020641738</v>
       </c>
       <c r="J9">
-        <v>140600.04200111047</v>
+        <v>28864.910083762261</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2">
-        <v>59327.717623552853</v>
+        <v>137108.97722321076</v>
       </c>
       <c r="D10">
-        <v>59822.431110027013</v>
+        <v>137672.80834832694</v>
       </c>
       <c r="E10">
-        <v>60272.377695399111</v>
+        <v>138122.72983772951</v>
       </c>
       <c r="F10">
-        <v>60734.269442776786</v>
+        <v>138587.59880102781</v>
       </c>
       <c r="G10">
-        <v>61233.088401521338</v>
+        <v>139178.941327529</v>
       </c>
       <c r="H10">
-        <v>61701.00872591394</v>
+        <v>139708.29743037571</v>
       </c>
       <c r="I10">
-        <v>62139.491398308237</v>
+        <v>140178.35169281636</v>
       </c>
       <c r="J10">
-        <v>62553.128540349266</v>
+        <v>140600.04200111047</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2">
-        <v>92686.07744882835</v>
+        <v>59327.717623552853</v>
       </c>
       <c r="D11">
-        <v>93533.113766653201</v>
+        <v>59822.431110027013</v>
       </c>
       <c r="E11">
-        <v>94301.416973208688</v>
+        <v>60272.377695399111</v>
       </c>
       <c r="F11">
-        <v>95083.403457660723</v>
+        <v>60734.269442776786</v>
       </c>
       <c r="G11">
-        <v>95915.376765816865</v>
+        <v>61233.088401521338</v>
       </c>
       <c r="H11">
-        <v>96711.644197366681</v>
+        <v>61701.00872591394</v>
       </c>
       <c r="I11">
-        <v>97473.905989773746</v>
+        <v>62139.491398308237</v>
       </c>
       <c r="J11">
-        <v>98211.040186110244</v>
+        <v>62553.128540349266</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2">
-        <v>69754.925417826904</v>
+        <v>92686.07744882835</v>
       </c>
       <c r="D12">
-        <v>70175.7090596669</v>
+        <v>93533.113766653201</v>
       </c>
       <c r="E12">
-        <v>70538.428465424542</v>
+        <v>94301.416973208688</v>
       </c>
       <c r="F12">
-        <v>70903.402855229433</v>
+        <v>95083.403457660723</v>
       </c>
       <c r="G12">
-        <v>71311.983025863214</v>
+        <v>95915.376765816865</v>
       </c>
       <c r="H12">
-        <v>71683.875584654554</v>
+        <v>96711.644197366681</v>
       </c>
       <c r="I12">
-        <v>72019.910306833015</v>
+        <v>97473.905989773746</v>
       </c>
       <c r="J12">
-        <v>72325.11473412234</v>
+        <v>98211.040186110244</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="2">
-        <v>21699.266475138473</v>
+        <v>69754.925417826904</v>
       </c>
       <c r="D13">
-        <v>21764.944155832291</v>
+        <v>70175.7090596669</v>
       </c>
       <c r="E13">
-        <v>21811.348623408179</v>
+        <v>70538.428465424542</v>
       </c>
       <c r="F13">
-        <v>21849.632913148314</v>
+        <v>70903.402855229433</v>
       </c>
       <c r="G13">
-        <v>21904.66063096351</v>
+        <v>71311.983025863214</v>
       </c>
       <c r="H13">
-        <v>21955.102915877673</v>
+        <v>71683.875584654554</v>
       </c>
       <c r="I13">
-        <v>21997.38940758512</v>
+        <v>72019.910306833015</v>
       </c>
       <c r="J13">
-        <v>22033.699211611452</v>
+        <v>72325.11473412234</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="2">
-        <v>83692.119332512375</v>
+        <v>21699.266475138473</v>
       </c>
       <c r="D14">
-        <v>83998.517424313904</v>
+        <v>21764.944155832291</v>
       </c>
       <c r="E14">
-        <v>84236.168027706211</v>
+        <v>21811.348623408179</v>
       </c>
       <c r="F14">
-        <v>84484.783081906207</v>
+        <v>21849.632913148314</v>
       </c>
       <c r="G14">
-        <v>84822.02859859429</v>
+        <v>21904.66063096351</v>
       </c>
       <c r="H14">
-        <v>85124.036623393782</v>
+        <v>21955.102915877673</v>
       </c>
       <c r="I14">
-        <v>85392.370603254356</v>
+        <v>21997.38940758512</v>
       </c>
       <c r="J14">
-        <v>85632.378177672275</v>
+        <v>22033.699211611452</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="2">
-        <v>61121.852323967265</v>
+        <v>83692.119332512375</v>
       </c>
       <c r="D15">
-        <v>61238.103433980854</v>
+        <v>83998.517424313904</v>
       </c>
       <c r="E15">
-        <v>61298.587848090203</v>
+        <v>84236.168027706211</v>
       </c>
       <c r="F15">
-        <v>61367.782723700424</v>
+        <v>84484.783081906207</v>
       </c>
       <c r="G15">
-        <v>61491.496604305343</v>
+        <v>84822.02859859429</v>
       </c>
       <c r="H15">
-        <v>61582.775444982355</v>
+        <v>85124.036623393782</v>
       </c>
       <c r="I15">
-        <v>61644.597169963599</v>
+        <v>85392.370603254356</v>
       </c>
       <c r="J15">
-        <v>61682.076522276198</v>
+        <v>85632.378177672275</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2">
-        <v>61401.434959428974</v>
+        <v>61121.852323967265</v>
       </c>
       <c r="D16">
-        <v>61375.276335137969</v>
+        <v>61238.103433980854</v>
       </c>
       <c r="E16">
-        <v>61300.468279927358</v>
+        <v>61298.587848090203</v>
       </c>
       <c r="F16">
-        <v>61222.141856896531</v>
+        <v>61367.782723700424</v>
       </c>
       <c r="G16">
-        <v>61219.858850544522</v>
+        <v>61491.496604305343</v>
       </c>
       <c r="H16">
-        <v>61195.410989207507</v>
+        <v>61582.775444982355</v>
       </c>
       <c r="I16">
-        <v>61146.352160207112</v>
+        <v>61644.597169963599</v>
       </c>
       <c r="J16">
-        <v>61075.892410603818</v>
+        <v>61682.076522276198</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2">
-        <v>7122.4202578776185</v>
+        <v>61401.434959428974</v>
       </c>
       <c r="D17">
-        <v>7170.1754347307342</v>
+        <v>61375.276335137969</v>
       </c>
       <c r="E17">
-        <v>7212.3979329465437</v>
+        <v>61300.468279927358</v>
       </c>
       <c r="F17">
-        <v>7254.2415825412281</v>
+        <v>61222.141856896531</v>
       </c>
       <c r="G17">
-        <v>7302.8764961520719</v>
+        <v>61219.858850544522</v>
       </c>
       <c r="H17">
-        <v>7350.5904790897384</v>
+        <v>61195.410989207507</v>
       </c>
       <c r="I17">
-        <v>7396.7790093970725</v>
+        <v>61146.352160207112</v>
       </c>
       <c r="J17">
-        <v>7441.7734689290855</v>
+        <v>61075.892410603818</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2">
-        <v>7759.3518669735276</v>
+        <v>7122.4202578776185</v>
       </c>
       <c r="D18">
-        <v>7771.0898506151243</v>
+        <v>7170.1754347307342</v>
       </c>
       <c r="E18">
-        <v>7775.0709125525045</v>
+        <v>7212.3979329465437</v>
       </c>
       <c r="F18">
-        <v>7780.3058970269703</v>
+        <v>7254.2415825412281</v>
       </c>
       <c r="G18">
-        <v>7790.8950646987632</v>
+        <v>7302.8764961520719</v>
       </c>
       <c r="H18">
-        <v>7798.4513862083104</v>
+        <v>7350.5904790897384</v>
       </c>
       <c r="I18">
-        <v>7803.6642829068005</v>
+        <v>7396.7790093970725</v>
       </c>
       <c r="J18">
-        <v>7807.6578448189439</v>
+        <v>7441.7734689290855</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="2">
-        <v>78069.636218031286</v>
+        <v>7759.3518669735276</v>
       </c>
       <c r="D19">
-        <v>78334.0228650551</v>
+        <v>7771.0898506151243</v>
       </c>
       <c r="E19">
-        <v>78531.415261871181</v>
+        <v>7775.0709125525045</v>
       </c>
       <c r="F19">
-        <v>78738.301687846397</v>
+        <v>7780.3058970269703</v>
       </c>
       <c r="G19">
-        <v>79005.003483688983</v>
+        <v>7790.8950646987632</v>
       </c>
       <c r="H19">
-        <v>79242.061353111261</v>
+        <v>7798.4513862083104</v>
       </c>
       <c r="I19">
-        <v>79446.274221882064</v>
+        <v>7803.6642829068005</v>
       </c>
       <c r="J19">
-        <v>79626.799403917961</v>
+        <v>7807.6578448189439</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="2">
-        <v>135629.67197663515</v>
+        <v>78069.636218031286</v>
       </c>
       <c r="D20">
-        <v>135309.07544926539</v>
+        <v>78334.0228650551</v>
       </c>
       <c r="E20">
-        <v>134888.72037859319</v>
+        <v>78531.415261871181</v>
       </c>
       <c r="F20">
-        <v>134518.01828420689</v>
+        <v>78738.301687846397</v>
       </c>
       <c r="G20">
-        <v>134255.78545538278</v>
+        <v>79005.003483688983</v>
       </c>
       <c r="H20">
-        <v>133935.42470404663</v>
+        <v>79242.061353111261</v>
       </c>
       <c r="I20">
-        <v>133565.67129016059</v>
+        <v>79446.274221882064</v>
       </c>
       <c r="J20">
-        <v>133160.3949137585</v>
+        <v>79626.799403917961</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="2">
-        <v>13110.005500423718</v>
+        <v>135629.67197663515</v>
       </c>
       <c r="D21">
-        <v>13183.729133336852</v>
+        <v>135309.07544926539</v>
       </c>
       <c r="E21">
-        <v>13246.651403262656</v>
+        <v>134888.72037859319</v>
       </c>
       <c r="F21">
-        <v>13307.452314695878</v>
+        <v>134518.01828420689</v>
       </c>
       <c r="G21">
-        <v>13378.597120763712</v>
+        <v>134255.78545538278</v>
       </c>
       <c r="H21">
-        <v>13444.785001561391</v>
+        <v>133935.42470404663</v>
       </c>
       <c r="I21">
-        <v>13504.034766530447</v>
+        <v>133565.67129016059</v>
       </c>
       <c r="J21">
-        <v>13556.817088881977</v>
+        <v>133160.3949137585</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="2">
-        <v>313360.92561695981</v>
+        <v>13110.005500423718</v>
       </c>
       <c r="D22">
-        <v>315839.75372438796</v>
+        <v>13183.729133336852</v>
       </c>
       <c r="E22">
-        <v>318088.6440784554</v>
+        <v>13246.651403262656</v>
       </c>
       <c r="F22">
-        <v>320443.52220739354</v>
+        <v>13307.452314695878</v>
       </c>
       <c r="G22">
-        <v>323050.18841104687</v>
+        <v>13378.597120763712</v>
       </c>
       <c r="H22">
-        <v>325535.31436990644</v>
+        <v>13444.785001561391</v>
       </c>
       <c r="I22">
-        <v>327910.92507413734</v>
+        <v>13504.034766530447</v>
       </c>
       <c r="J22">
-        <v>330205.17742366367</v>
+        <v>13556.817088881977</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="2">
-        <v>89238.4691379383</v>
+        <v>313360.92561695981</v>
       </c>
       <c r="D23">
-        <v>89751.117726494733</v>
+        <v>315839.75372438796</v>
       </c>
       <c r="E23">
-        <v>90222.592378455636</v>
+        <v>318088.6440784554</v>
       </c>
       <c r="F23">
-        <v>90734.977236801933</v>
+        <v>320443.52220739354</v>
       </c>
       <c r="G23">
-        <v>91347.60438278153</v>
+        <v>323050.18841104687</v>
       </c>
       <c r="H23">
-        <v>91936.254256840053</v>
+        <v>325535.31436990644</v>
       </c>
       <c r="I23">
-        <v>92499.330742835184</v>
+        <v>327910.92507413734</v>
       </c>
       <c r="J23">
-        <v>93040.45987959209</v>
+        <v>330205.17742366367</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24" s="2">
-        <v>77877.077161967609</v>
+        <v>89238.4691379383</v>
       </c>
       <c r="D24">
-        <v>78403.786442124343</v>
+        <v>89751.117726494733</v>
       </c>
       <c r="E24">
-        <v>78869.704837408732</v>
+        <v>90222.592378455636</v>
       </c>
       <c r="F24">
-        <v>79353.711624637595</v>
+        <v>90734.977236801933</v>
       </c>
       <c r="G24">
-        <v>79903.351358818385</v>
+        <v>91347.60438278153</v>
       </c>
       <c r="H24">
-        <v>80425.377734916896</v>
+        <v>91936.254256840053</v>
       </c>
       <c r="I24">
-        <v>80918.034030608338</v>
+        <v>92499.330742835184</v>
       </c>
       <c r="J24">
-        <v>81388.212901806168</v>
+        <v>93040.45987959209</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="2">
-        <v>7320.929017146681</v>
+        <v>77877.077161967609</v>
       </c>
       <c r="D25">
-        <v>7361.0757416480046</v>
+        <v>78403.786442124343</v>
       </c>
       <c r="E25">
-        <v>7394.6359396497583</v>
+        <v>78869.704837408732</v>
       </c>
       <c r="F25">
-        <v>7426.0700961330249</v>
+        <v>79353.711624637595</v>
       </c>
       <c r="G25">
-        <v>7466.9570767604164</v>
+        <v>79903.351358818385</v>
       </c>
       <c r="H25">
-        <v>7506.6766861686046</v>
+        <v>80425.377734916896</v>
       </c>
       <c r="I25">
-        <v>7544.0483142238791</v>
+        <v>80918.034030608338</v>
       </c>
       <c r="J25">
-        <v>7579.5317810666347</v>
+        <v>81388.212901806168</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26" s="2">
-        <v>29541.082982532505</v>
+        <v>7320.929017146681</v>
       </c>
       <c r="D26">
-        <v>29717.805638599453</v>
+        <v>7361.0757416480046</v>
       </c>
       <c r="E26">
-        <v>29868.143157312552</v>
+        <v>7394.6359396497583</v>
       </c>
       <c r="F26">
-        <v>30023.04436437945</v>
+        <v>7426.0700961330249</v>
       </c>
       <c r="G26">
-        <v>30211.450794485689</v>
+        <v>7466.9570767604164</v>
       </c>
       <c r="H26">
-        <v>30387.010915394148</v>
+        <v>7506.6766861686046</v>
       </c>
       <c r="I26">
-        <v>30549.631443968738</v>
+        <v>7544.0483142238791</v>
       </c>
       <c r="J26">
-        <v>30700.887241410855</v>
+        <v>7579.5317810666347</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="2">
-        <v>48765.107980937304</v>
+        <v>29541.082982532505</v>
       </c>
       <c r="D27">
-        <v>49043.284590456722</v>
+        <v>29717.805638599453</v>
       </c>
       <c r="E27">
-        <v>49281.803857867621</v>
+        <v>29868.143157312552</v>
       </c>
       <c r="F27">
-        <v>49533.390797896165</v>
+        <v>30023.04436437945</v>
       </c>
       <c r="G27">
-        <v>49824.75609697136</v>
+        <v>30211.450794485689</v>
       </c>
       <c r="H27">
-        <v>50096.694959167653</v>
+        <v>30387.010915394148</v>
       </c>
       <c r="I27">
-        <v>50352.177965831739</v>
+        <v>30549.631443968738</v>
       </c>
       <c r="J27">
-        <v>50596.002008162366</v>
+        <v>30700.887241410855</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2">
-        <v>40963.256483213729</v>
+        <v>48765.107980937304</v>
       </c>
       <c r="D28">
-        <v>41276.89223737485</v>
+        <v>49043.284590456722</v>
       </c>
       <c r="E28">
-        <v>41554.634450873666</v>
+        <v>49281.803857867621</v>
       </c>
       <c r="F28">
-        <v>41836.698631271211</v>
+        <v>49533.390797896165</v>
       </c>
       <c r="G28">
-        <v>42154.899824518216</v>
+        <v>49824.75609697136</v>
       </c>
       <c r="H28">
-        <v>42451.974203365389</v>
+        <v>50096.694959167653</v>
       </c>
       <c r="I28">
-        <v>42728.058070289349</v>
+        <v>50352.177965831739</v>
       </c>
       <c r="J28">
-        <v>42985.942364186834</v>
+        <v>50596.002008162366</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="2">
-        <v>33882.600982043499</v>
+        <v>40963.256483213729</v>
       </c>
       <c r="D29">
-        <v>34176.470268437144</v>
+        <v>41276.89223737485</v>
       </c>
       <c r="E29">
-        <v>34445.219792297896</v>
+        <v>41554.634450873666</v>
       </c>
       <c r="F29">
-        <v>34724.767891031428</v>
+        <v>41836.698631271211</v>
       </c>
       <c r="G29">
-        <v>35031.420491939141</v>
+        <v>42154.899824518216</v>
       </c>
       <c r="H29">
-        <v>35326.388041990387</v>
+        <v>42451.974203365389</v>
       </c>
       <c r="I29">
-        <v>35610.729045535874</v>
+        <v>42728.058070289349</v>
       </c>
       <c r="J29">
-        <v>35887.50629408886</v>
+        <v>42985.942364186834</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" s="2">
-        <v>23883.945695728271</v>
+        <v>33882.600982043499</v>
       </c>
       <c r="D30">
-        <v>24108.793118878952</v>
+        <v>34176.470268437144</v>
       </c>
       <c r="E30">
-        <v>24314.980402740177</v>
+        <v>34445.219792297896</v>
       </c>
       <c r="F30">
-        <v>24529.190363262773</v>
+        <v>34724.767891031428</v>
       </c>
       <c r="G30">
-        <v>24765.852742959367</v>
+        <v>35031.420491939141</v>
       </c>
       <c r="H30">
-        <v>24995.111360903808</v>
+        <v>35326.388041990387</v>
       </c>
       <c r="I30">
-        <v>25216.704662382457</v>
+        <v>35610.729045535874</v>
       </c>
       <c r="J30">
-        <v>25432.670833095552</v>
+        <v>35887.50629408886</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31" s="2">
-        <v>200446.33903553456</v>
+        <v>23883.945695728271</v>
       </c>
       <c r="D31">
-        <v>202460.44574270881</v>
+        <v>24108.793118878952</v>
       </c>
       <c r="E31">
-        <v>204279.69378021406</v>
+        <v>24314.980402740177</v>
       </c>
       <c r="F31">
-        <v>206137.18581285374</v>
+        <v>24529.190363262773</v>
       </c>
       <c r="G31">
-        <v>208090.04377414947</v>
+        <v>24765.852742959367</v>
       </c>
       <c r="H31">
-        <v>209952.36142776033</v>
+        <v>24995.111360903808</v>
       </c>
       <c r="I31">
-        <v>211734.55657996901</v>
+        <v>25216.704662382457</v>
       </c>
       <c r="J31">
-        <v>213462.05760644379</v>
+        <v>25432.670833095552</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" s="2">
-        <v>14410.500892204112</v>
+        <v>200446.33903553456</v>
       </c>
       <c r="D32">
-        <v>14491.923034722011</v>
+        <v>202460.44574270881</v>
       </c>
       <c r="E32">
-        <v>14558.853311469073</v>
+        <v>204279.69378021406</v>
       </c>
       <c r="F32">
-        <v>14625.908688425683</v>
+        <v>206137.18581285374</v>
       </c>
       <c r="G32">
-        <v>14702.808933728729</v>
+        <v>208090.04377414947</v>
       </c>
       <c r="H32">
-        <v>14775.258891729212</v>
+        <v>209952.36142776033</v>
       </c>
       <c r="I32">
-        <v>14842.218408954172</v>
+        <v>211734.55657996901</v>
       </c>
       <c r="J32">
-        <v>14905.718577626563</v>
+        <v>213462.05760644379</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" s="2">
-        <v>22165.483844052134</v>
+        <v>14410.500892204112</v>
       </c>
       <c r="D33">
-        <v>22286.742297299294</v>
+        <v>14491.923034722011</v>
       </c>
       <c r="E33">
-        <v>22389.893596095448</v>
+        <v>14558.853311469073</v>
       </c>
       <c r="F33">
-        <v>22495.123697400486</v>
+        <v>14625.908688425683</v>
       </c>
       <c r="G33">
-        <v>22618.636118456088</v>
+        <v>14702.808933728729</v>
       </c>
       <c r="H33">
-        <v>22736.141499495548</v>
+        <v>14775.258891729212</v>
       </c>
       <c r="I33">
-        <v>22845.901334634611</v>
+        <v>14842.218408954172</v>
       </c>
       <c r="J33">
-        <v>22949.724314421946</v>
+        <v>14905.718577626563</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34" s="2">
-        <v>54442.633617922635</v>
+        <v>22165.483844052134</v>
       </c>
       <c r="D34">
-        <v>54914.484400481932</v>
+        <v>22286.742297299294</v>
       </c>
       <c r="E34">
-        <v>55327.380185659931</v>
+        <v>22389.893596095448</v>
       </c>
       <c r="F34">
-        <v>55742.077547918117</v>
+        <v>22495.123697400486</v>
       </c>
       <c r="G34">
-        <v>56183.300785400308</v>
+        <v>22618.636118456088</v>
       </c>
       <c r="H34">
-        <v>56595.672709340695</v>
+        <v>22736.141499495548</v>
       </c>
       <c r="I34">
-        <v>56979.646899505606</v>
+        <v>22845.901334634611</v>
       </c>
       <c r="J34">
-        <v>57342.204427995886</v>
+        <v>22949.724314421946</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" s="2">
-        <v>34045.178955669733</v>
+        <v>54442.633617922635</v>
       </c>
       <c r="D35">
-        <v>34613.322333999757</v>
+        <v>54914.484400481932</v>
       </c>
       <c r="E35">
-        <v>35155.569166521127</v>
+        <v>55327.380185659931</v>
       </c>
       <c r="F35">
-        <v>35705.867328374829</v>
+        <v>55742.077547918117</v>
       </c>
       <c r="G35">
-        <v>36273.280770196085</v>
+        <v>56183.300785400308</v>
       </c>
       <c r="H35">
-        <v>36830.329542730105</v>
+        <v>56595.672709340695</v>
       </c>
       <c r="I35">
-        <v>37377.746291319643</v>
+        <v>56979.646899505606</v>
       </c>
       <c r="J35">
-        <v>37920.982549846267</v>
+        <v>57342.204427995886</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" s="2">
-        <v>19166.649236339777</v>
+        <v>34045.178955669733</v>
       </c>
       <c r="D36">
-        <v>19321.120454714626</v>
+        <v>34613.322333999757</v>
       </c>
       <c r="E36">
-        <v>19455.622382527719</v>
+        <v>35155.569166521127</v>
       </c>
       <c r="F36">
-        <v>19591.597665289206</v>
+        <v>35705.867328374829</v>
       </c>
       <c r="G36">
-        <v>19734.915436377654</v>
+        <v>36273.280770196085</v>
       </c>
       <c r="H36">
-        <v>19867.643638997855</v>
+        <v>36830.329542730105</v>
       </c>
       <c r="I36">
-        <v>19990.282694789319</v>
+        <v>37377.746291319643</v>
       </c>
       <c r="J36">
-        <v>20105.116140972168</v>
+        <v>37920.982549846267</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C37" s="2">
-        <v>16589.593831471066</v>
+        <v>19166.649236339777</v>
       </c>
       <c r="D37">
-        <v>16827.182967563109</v>
+        <v>19321.120454714626</v>
       </c>
       <c r="E37">
-        <v>17051.788503922038</v>
+        <v>19455.622382527719</v>
       </c>
       <c r="F37">
-        <v>17287.301265290902</v>
+        <v>19591.597665289206</v>
       </c>
       <c r="G37">
-        <v>17535.050964030685</v>
+        <v>19734.915436377654</v>
       </c>
       <c r="H37">
-        <v>17781.490271297116</v>
+        <v>19867.643638997855</v>
       </c>
       <c r="I37">
-        <v>18028.854551626591</v>
+        <v>19990.282694789319</v>
       </c>
       <c r="J37">
-        <v>18280.858485204506</v>
+        <v>20105.116140972168</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="2">
-        <v>301</v>
+        <v>216</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C38" s="2">
-        <v>160800.54777507891</v>
+        <v>16589.593831471066</v>
       </c>
       <c r="D38">
-        <v>161280.42527189513</v>
+        <v>16827.182967563109</v>
       </c>
       <c r="E38">
-        <v>161627.97671123757</v>
+        <v>17051.788503922038</v>
       </c>
       <c r="F38">
-        <v>162000.70559117768</v>
+        <v>17287.301265290902</v>
       </c>
       <c r="G38">
-        <v>162496.67500110657</v>
+        <v>17535.050964030685</v>
       </c>
       <c r="H38">
-        <v>162917.63405208182</v>
+        <v>17781.490271297116</v>
       </c>
       <c r="I38">
-        <v>163270.926310829</v>
+        <v>18028.854551626591</v>
       </c>
       <c r="J38">
-        <v>163572.10229544528</v>
+        <v>18280.858485204506</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" s="2">
-        <v>60503.614472114554</v>
+        <v>160800.54777507891</v>
       </c>
       <c r="D39">
-        <v>60717.003226983506</v>
+        <v>161280.42527189513</v>
       </c>
       <c r="E39">
-        <v>60877.90716440152</v>
+        <v>161627.97671123757</v>
       </c>
       <c r="F39">
-        <v>61043.883481112134</v>
+        <v>162000.70559117768</v>
       </c>
       <c r="G39">
-        <v>61242.217357950612</v>
+        <v>162496.67500110657</v>
       </c>
       <c r="H39">
-        <v>61406.745134117235</v>
+        <v>162917.63405208182</v>
       </c>
       <c r="I39">
-        <v>61541.932587074436</v>
+        <v>163270.926310829</v>
       </c>
       <c r="J39">
-        <v>61653.97474301036</v>
+        <v>163572.10229544528</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C40" s="2">
-        <v>111181.99268416413</v>
+        <v>60503.614472114554</v>
       </c>
       <c r="D40">
-        <v>111766.04451706965</v>
+        <v>60717.003226983506</v>
       </c>
       <c r="E40">
-        <v>112255.12819865815</v>
+        <v>60877.90716440152</v>
       </c>
       <c r="F40">
-        <v>112765.23437957227</v>
+        <v>61043.883481112134</v>
       </c>
       <c r="G40">
-        <v>113339.91833670542</v>
+        <v>61242.217357950612</v>
       </c>
       <c r="H40">
-        <v>113862.04590935982</v>
+        <v>61406.745134117235</v>
       </c>
       <c r="I40">
-        <v>114333.26044229898</v>
+        <v>61541.932587074436</v>
       </c>
       <c r="J40">
-        <v>114762.87111777262</v>
+        <v>61653.97474301036</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="2">
-        <v>16013.572967355041</v>
+        <v>111181.99268416413</v>
       </c>
       <c r="D41">
-        <v>15977.181021494474</v>
+        <v>111766.04451706965</v>
       </c>
       <c r="E41">
-        <v>15926.746007227754</v>
+        <v>112255.12819865815</v>
       </c>
       <c r="F41">
-        <v>15880.863099543236</v>
+        <v>112765.23437957227</v>
       </c>
       <c r="G41">
-        <v>15849.20884603378</v>
+        <v>113339.91833670542</v>
       </c>
       <c r="H41">
-        <v>15810.960242700505</v>
+        <v>113862.04590935982</v>
       </c>
       <c r="I41">
-        <v>15767.444766167133</v>
+        <v>114333.26044229898</v>
       </c>
       <c r="J41">
-        <v>15720.473399737813</v>
+        <v>114762.87111777262</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C42" s="2">
-        <v>70325.525267318735</v>
+        <v>16013.572967355041</v>
       </c>
       <c r="D42">
-        <v>70071.002504341726</v>
+        <v>15977.181021494474</v>
       </c>
       <c r="E42">
-        <v>69757.467252144503</v>
+        <v>15926.746007227754</v>
       </c>
       <c r="F42">
-        <v>69454.399165041454</v>
+        <v>15880.863099543236</v>
       </c>
       <c r="G42">
-        <v>69224.730449347262</v>
+        <v>15849.20884603378</v>
       </c>
       <c r="H42">
-        <v>68965.472008065815</v>
+        <v>15810.960242700505</v>
       </c>
       <c r="I42">
-        <v>68677.29704757547</v>
+        <v>15767.444766167133</v>
       </c>
       <c r="J42">
-        <v>68365.928622810781</v>
+        <v>15720.473399737813</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C43" s="2">
-        <v>15059.088779095084</v>
+        <v>70325.525267318735</v>
       </c>
       <c r="D43">
-        <v>15089.387764805415</v>
+        <v>70071.002504341726</v>
       </c>
       <c r="E43">
-        <v>15106.38659159746</v>
+        <v>69757.467252144503</v>
       </c>
       <c r="F43">
-        <v>15126.287834879924</v>
+        <v>69454.399165041454</v>
       </c>
       <c r="G43">
-        <v>15156.658024167828</v>
+        <v>69224.730449347262</v>
       </c>
       <c r="H43">
-        <v>15180.497352227827</v>
+        <v>68965.472008065815</v>
       </c>
       <c r="I43">
-        <v>15197.918147594393</v>
+        <v>68677.29704757547</v>
       </c>
       <c r="J43">
-        <v>15210.607927978965</v>
+        <v>68365.928622810781</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44" s="2">
-        <v>48159.580867468983</v>
+        <v>15059.088779095084</v>
       </c>
       <c r="D44">
-        <v>48301.73118490263</v>
+        <v>15089.387764805415</v>
       </c>
       <c r="E44">
-        <v>48402.311033166268</v>
+        <v>15106.38659159746</v>
       </c>
       <c r="F44">
-        <v>48509.648289842356</v>
+        <v>15126.287834879924</v>
       </c>
       <c r="G44">
-        <v>48643.742912462461</v>
+        <v>15156.658024167828</v>
       </c>
       <c r="H44">
-        <v>48752.566329069894</v>
+        <v>15180.497352227827</v>
       </c>
       <c r="I44">
-        <v>48838.159453468536</v>
+        <v>15197.918147594393</v>
       </c>
       <c r="J44">
-        <v>48904.820942035687</v>
+        <v>15210.607927978965</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" s="2">
-        <v>44512.114468701118</v>
+        <v>48159.580867468983</v>
       </c>
       <c r="D45">
-        <v>44666.915478930954</v>
+        <v>48301.73118490263</v>
       </c>
       <c r="E45">
-        <v>44784.542621554501</v>
+        <v>48402.311033166268</v>
       </c>
       <c r="F45">
-        <v>44909.378539662881</v>
+        <v>48509.648289842356</v>
       </c>
       <c r="G45">
-        <v>45056.486884184036</v>
+        <v>48643.742912462461</v>
       </c>
       <c r="H45">
-        <v>45181.162209912465</v>
+        <v>48752.566329069894</v>
       </c>
       <c r="I45">
-        <v>45285.902788606807</v>
+        <v>48838.159453468536</v>
       </c>
       <c r="J45">
-        <v>45374.968043115667</v>
+        <v>48904.820942035687</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="2">
-        <v>401</v>
+        <v>308</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" s="2">
-        <v>141279.33236905705</v>
+        <v>44512.114468701118</v>
       </c>
       <c r="D46">
-        <v>142202.25641828633</v>
+        <v>44666.915478930954</v>
       </c>
       <c r="E46">
-        <v>143023.27400782524</v>
+        <v>44784.542621554501</v>
       </c>
       <c r="F46">
-        <v>143878.59181499912</v>
+        <v>44909.378539662881</v>
       </c>
       <c r="G46">
-        <v>144847.03447788698</v>
+        <v>45056.486884184036</v>
       </c>
       <c r="H46">
-        <v>145753.17484595999</v>
+        <v>45181.162209912465</v>
       </c>
       <c r="I46">
-        <v>146599.63076023583</v>
+        <v>45285.902788606807</v>
       </c>
       <c r="J46">
-        <v>147395.18778828083</v>
+        <v>45374.968043115667</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C47" s="2">
-        <v>46412.577574639348</v>
+        <v>141279.33236905705</v>
       </c>
       <c r="D47">
-        <v>46837.715303119548</v>
+        <v>142202.25641828633</v>
       </c>
       <c r="E47">
-        <v>47228.366173482646</v>
+        <v>143023.27400782524</v>
       </c>
       <c r="F47">
-        <v>47623.018901271993</v>
+        <v>143878.59181499912</v>
       </c>
       <c r="G47">
-        <v>48048.298272305838</v>
+        <v>144847.03447788698</v>
       </c>
       <c r="H47">
-        <v>48455.416476137078</v>
+        <v>145753.17484595999</v>
       </c>
       <c r="I47">
-        <v>48843.327963922216</v>
+        <v>146599.63076023583</v>
       </c>
       <c r="J47">
-        <v>49215.938205570419</v>
+        <v>147395.18778828083</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48" s="2">
-        <v>48618.467107528188</v>
+        <v>46412.577574639348</v>
       </c>
       <c r="D48">
-        <v>48874.037335342255</v>
+        <v>46837.715303119548</v>
       </c>
       <c r="E48">
-        <v>49088.620451033275</v>
+        <v>47228.366173482646</v>
       </c>
       <c r="F48">
-        <v>49308.19975070958</v>
+        <v>47623.018901271993</v>
       </c>
       <c r="G48">
-        <v>49575.27052620006</v>
+        <v>48048.298272305838</v>
       </c>
       <c r="H48">
-        <v>49815.72831484754</v>
+        <v>48455.416476137078</v>
       </c>
       <c r="I48">
-        <v>50030.592737469102</v>
+        <v>48843.327963922216</v>
       </c>
       <c r="J48">
-        <v>50222.035959988832</v>
+        <v>49215.938205570419</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" s="2">
-        <v>42982.873210465354</v>
+        <v>48618.467107528188</v>
       </c>
       <c r="D49">
-        <v>43365.146660517436</v>
+        <v>48874.037335342255</v>
       </c>
       <c r="E49">
-        <v>43715.780159724323</v>
+        <v>49088.620451033275</v>
       </c>
       <c r="F49">
-        <v>44052.55657600081</v>
+        <v>49308.19975070958</v>
       </c>
       <c r="G49">
-        <v>44406.251422455272</v>
+        <v>49575.27052620006</v>
       </c>
       <c r="H49">
-        <v>44769.244883051353</v>
+        <v>49815.72831484754</v>
       </c>
       <c r="I49">
-        <v>45118.850770027988</v>
+        <v>50030.592737469102</v>
       </c>
       <c r="J49">
-        <v>45462.561225169775</v>
+        <v>50222.035959988832</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C50" s="2">
-        <v>54313.580033103179</v>
+        <v>42982.873210465354</v>
       </c>
       <c r="D50">
-        <v>54734.025406029439</v>
+        <v>43365.146660517436</v>
       </c>
       <c r="E50">
-        <v>55115.807508508457</v>
+        <v>43715.780159724323</v>
       </c>
       <c r="F50">
-        <v>55512.768544540959</v>
+        <v>44052.55657600081</v>
       </c>
       <c r="G50">
-        <v>55951.543694382271</v>
+        <v>44406.251422455272</v>
       </c>
       <c r="H50">
-        <v>56366.597596674619</v>
+        <v>44769.244883051353</v>
       </c>
       <c r="I50">
-        <v>56759.687014512048</v>
+        <v>45118.850770027988</v>
       </c>
       <c r="J50">
-        <v>57133.870253866073</v>
+        <v>45462.561225169775</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C51" s="2">
-        <v>22740.240755341045</v>
+        <v>54313.580033103179</v>
       </c>
       <c r="D51">
-        <v>22878.719231396019</v>
+        <v>54734.025406029439</v>
       </c>
       <c r="E51">
-        <v>22998.820806548752</v>
+        <v>55115.807508508457</v>
       </c>
       <c r="F51">
-        <v>23114.718527135763</v>
+        <v>55512.768544540959</v>
       </c>
       <c r="G51">
-        <v>23247.741080762811</v>
+        <v>55951.543694382271</v>
       </c>
       <c r="H51">
-        <v>23372.149792088916</v>
+        <v>56366.597596674619</v>
       </c>
       <c r="I51">
-        <v>23486.53106453568</v>
+        <v>56759.687014512048</v>
       </c>
       <c r="J51">
-        <v>23592.416168728461</v>
+        <v>57133.870253866073</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C52" s="2">
-        <v>25802.988492663877</v>
+        <v>22740.240755341045</v>
       </c>
       <c r="D52">
-        <v>25941.173686726754</v>
+        <v>22878.719231396019</v>
       </c>
       <c r="E52">
-        <v>26059.840980003042</v>
+        <v>22998.820806548752</v>
       </c>
       <c r="F52">
-        <v>26163.757816213627</v>
+        <v>23114.718527135763</v>
       </c>
       <c r="G52">
-        <v>26281.924715577396</v>
+        <v>23247.741080762811</v>
       </c>
       <c r="H52">
-        <v>26400.43631688433</v>
+        <v>23372.149792088916</v>
       </c>
       <c r="I52">
-        <v>26506.897045494108</v>
+        <v>23486.53106453568</v>
       </c>
       <c r="J52">
-        <v>26604.690769632267</v>
+        <v>23592.416168728461</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C53" s="2">
-        <v>21193.070036267593</v>
+        <v>25802.988492663877</v>
       </c>
       <c r="D53">
-        <v>21368.590451956381</v>
+        <v>25941.173686726754</v>
       </c>
       <c r="E53">
-        <v>21526.137691364791</v>
+        <v>26059.840980003042</v>
       </c>
       <c r="F53">
-        <v>21680.534022475385</v>
+        <v>26163.757816213627</v>
       </c>
       <c r="G53">
-        <v>21851.195489832637</v>
+        <v>26281.924715577396</v>
       </c>
       <c r="H53">
-        <v>22009.657897121673</v>
+        <v>26400.43631688433</v>
       </c>
       <c r="I53">
-        <v>22155.700246106757</v>
+        <v>26506.897045494108</v>
       </c>
       <c r="J53">
-        <v>22289.956242268658</v>
+        <v>26604.690769632267</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C54" s="2">
-        <v>30125.956695576082</v>
+        <v>21193.070036267593</v>
       </c>
       <c r="D54">
-        <v>30197.445043270716</v>
+        <v>21368.590451956381</v>
       </c>
       <c r="E54">
-        <v>30245.175504739684</v>
+        <v>21526.137691364791</v>
       </c>
       <c r="F54">
-        <v>30289.356996341143</v>
+        <v>21680.534022475385</v>
       </c>
       <c r="G54">
-        <v>30358.833333149756</v>
+        <v>21851.195489832637</v>
       </c>
       <c r="H54">
-        <v>30413.045743865176</v>
+        <v>22009.657897121673</v>
       </c>
       <c r="I54">
-        <v>30452.096574756833</v>
+        <v>22155.700246106757</v>
       </c>
       <c r="J54">
-        <v>30477.652583952695</v>
+        <v>22289.956242268658</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C55" s="2">
-        <v>86102.105355116975</v>
+        <v>30125.956695576082</v>
       </c>
       <c r="D55">
-        <v>87846.011448865989</v>
+        <v>30197.445043270716</v>
       </c>
       <c r="E55">
-        <v>89523.152601791604</v>
+        <v>30245.175504739684</v>
       </c>
       <c r="F55">
-        <v>91247.18921648222</v>
+        <v>30289.356996341143</v>
       </c>
       <c r="G55">
-        <v>93011.848265416396</v>
+        <v>30358.833333149756</v>
       </c>
       <c r="H55">
-        <v>94754.303571202909</v>
+        <v>30413.045743865176</v>
       </c>
       <c r="I55">
-        <v>96484.759249818453</v>
+        <v>30452.096574756833</v>
       </c>
       <c r="J55">
-        <v>98218.675895166904</v>
+        <v>30477.652583952695</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="2">
-        <v>501</v>
+        <v>410</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C56" s="2">
-        <v>76113.681382974697</v>
+        <v>86102.105355116975</v>
       </c>
       <c r="D56">
-        <v>77096.296252818574</v>
+        <v>87846.011448865989</v>
       </c>
       <c r="E56">
-        <v>78009.749847447587</v>
+        <v>89523.152601791604</v>
       </c>
       <c r="F56">
-        <v>78932.309226287092</v>
+        <v>91247.18921648222</v>
       </c>
       <c r="G56">
-        <v>79888.486997056185</v>
+        <v>93011.848265416396</v>
       </c>
       <c r="H56">
-        <v>80807.241453146038</v>
+        <v>94754.303571202909</v>
       </c>
       <c r="I56">
-        <v>81692.633378876577</v>
+        <v>96484.759249818453</v>
       </c>
       <c r="J56">
-        <v>82554.658882824282</v>
+        <v>98218.675895166904</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C57" s="2">
-        <v>57161.818517786087</v>
+        <v>76113.681382974697</v>
       </c>
       <c r="D57">
-        <v>57469.263385984261</v>
+        <v>77096.296252818574</v>
       </c>
       <c r="E57">
-        <v>57726.741389682909</v>
+        <v>78009.749847447587</v>
       </c>
       <c r="F57">
-        <v>57990.64272807278</v>
+        <v>78932.309226287092</v>
       </c>
       <c r="G57">
-        <v>58328.621459000417</v>
+        <v>79888.486997056185</v>
       </c>
       <c r="H57">
-        <v>58648.803653638912</v>
+        <v>80807.241453146038</v>
       </c>
       <c r="I57">
-        <v>58951.174854180565</v>
+        <v>81692.633378876577</v>
       </c>
       <c r="J57">
-        <v>59240.650304586241</v>
+        <v>82554.658882824282</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C58" s="2">
-        <v>68302.663687150722</v>
+        <v>57161.818517786087</v>
       </c>
       <c r="D58">
-        <v>69154.674022621562</v>
+        <v>57469.263385984261</v>
       </c>
       <c r="E58">
-        <v>69947.621239541128</v>
+        <v>57726.741389682909</v>
       </c>
       <c r="F58">
-        <v>70743.510211495974</v>
+        <v>57990.64272807278</v>
       </c>
       <c r="G58">
-        <v>71602.917411404254</v>
+        <v>58328.621459000417</v>
       </c>
       <c r="H58">
-        <v>72442.974913997023</v>
+        <v>58648.803653638912</v>
       </c>
       <c r="I58">
-        <v>73259.612882649904</v>
+        <v>58951.174854180565</v>
       </c>
       <c r="J58">
-        <v>74058.837080034005</v>
+        <v>59240.650304586241</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C59" s="2">
-        <v>24209.971915413378</v>
+        <v>68302.663687150722</v>
       </c>
       <c r="D59">
-        <v>24453.80710689459</v>
+        <v>69154.674022621562</v>
       </c>
       <c r="E59">
-        <v>24676.028489741897</v>
+        <v>69947.621239541128</v>
       </c>
       <c r="F59">
-        <v>24906.165998362354</v>
+        <v>70743.510211495974</v>
       </c>
       <c r="G59">
-        <v>25153.296270303981</v>
+        <v>71602.917411404254</v>
       </c>
       <c r="H59">
-        <v>25390.600989713632</v>
+        <v>72442.974913997023</v>
       </c>
       <c r="I59">
-        <v>25619.652219474352</v>
+        <v>73259.612882649904</v>
       </c>
       <c r="J59">
-        <v>25844.101482311409</v>
+        <v>74058.837080034005</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C60" s="2">
-        <v>46040.071352808089</v>
+        <v>24209.971915413378</v>
       </c>
       <c r="D60">
-        <v>46685.735346013011</v>
+        <v>24453.80710689459</v>
       </c>
       <c r="E60">
-        <v>47295.547543848763</v>
+        <v>24676.028489741897</v>
       </c>
       <c r="F60">
-        <v>47920.35288895783</v>
+        <v>24906.165998362354</v>
       </c>
       <c r="G60">
-        <v>48582.931724510723</v>
+        <v>25153.296270303981</v>
       </c>
       <c r="H60">
-        <v>49230.883965853231</v>
+        <v>25390.600989713632</v>
       </c>
       <c r="I60">
-        <v>49867.478430697767</v>
+        <v>25619.652219474352</v>
       </c>
       <c r="J60">
-        <v>50498.807069528542</v>
+        <v>25844.101482311409</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C61" s="2">
-        <v>31572.870195090771</v>
+        <v>46040.071352808089</v>
       </c>
       <c r="D61">
-        <v>31793.420357465693</v>
+        <v>46685.735346013011</v>
       </c>
       <c r="E61">
-        <v>31981.265358514702</v>
+        <v>47295.547543848763</v>
       </c>
       <c r="F61">
-        <v>32170.768383659823</v>
+        <v>47920.35288895783</v>
       </c>
       <c r="G61">
-        <v>32375.7318006532</v>
+        <v>48582.931724510723</v>
       </c>
       <c r="H61">
-        <v>32561.982938915993</v>
+        <v>49230.883965853231</v>
       </c>
       <c r="I61">
-        <v>32731.377204821736</v>
+        <v>49867.478430697767</v>
       </c>
       <c r="J61">
-        <v>32887.959013139814</v>
+        <v>50498.807069528542</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C62" s="2">
-        <v>19885.432570915815</v>
+        <v>31572.870195090771</v>
       </c>
       <c r="D62">
-        <v>19927.92901809324</v>
+        <v>31793.420357465693</v>
       </c>
       <c r="E62">
-        <v>19952.168150931611</v>
+        <v>31981.265358514702</v>
       </c>
       <c r="F62">
-        <v>19980.110714993098</v>
+        <v>32170.768383659823</v>
       </c>
       <c r="G62">
-        <v>20026.211315479628</v>
+        <v>32375.7318006532</v>
       </c>
       <c r="H62">
-        <v>20064.67510338538</v>
+        <v>32561.982938915993</v>
       </c>
       <c r="I62">
-        <v>20095.802816900716</v>
+        <v>32731.377204821736</v>
       </c>
       <c r="J62">
-        <v>20122.166278992339</v>
+        <v>32887.959013139814</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C63" s="2">
-        <v>24550.259070555054</v>
+        <v>19885.432570915815</v>
       </c>
       <c r="D63">
-        <v>24615.81322138794</v>
+        <v>19927.92901809324</v>
       </c>
       <c r="E63">
-        <v>24655.670055607909</v>
+        <v>19952.168150931611</v>
       </c>
       <c r="F63">
-        <v>24692.647598120115</v>
+        <v>19980.110714993098</v>
       </c>
       <c r="G63">
-        <v>24757.05625956774</v>
+        <v>20026.211315479628</v>
       </c>
       <c r="H63">
-        <v>24813.998999688454</v>
+        <v>20064.67510338538</v>
       </c>
       <c r="I63">
-        <v>24860.439645587783</v>
+        <v>20095.802816900716</v>
       </c>
       <c r="J63">
-        <v>24898.729372610163</v>
+        <v>20122.166278992339</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C64" s="2">
-        <v>11475.207717340756</v>
+        <v>24550.259070555054</v>
       </c>
       <c r="D64">
-        <v>11488.700872741154</v>
+        <v>24615.81322138794</v>
       </c>
       <c r="E64">
-        <v>11487.650047520421</v>
+        <v>24655.670055607909</v>
       </c>
       <c r="F64">
-        <v>11472.984368819536</v>
+        <v>24692.647598120115</v>
       </c>
       <c r="G64">
-        <v>11471.694809933386</v>
+        <v>24757.05625956774</v>
       </c>
       <c r="H64">
-        <v>11469.054724813679</v>
+        <v>24813.998999688454</v>
       </c>
       <c r="I64">
-        <v>11460.640697119017</v>
+        <v>24860.439645587783</v>
       </c>
       <c r="J64">
-        <v>11446.434468706462</v>
+        <v>24898.729372610163</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C65" s="2">
-        <v>26061.852712436965</v>
+        <v>11475.207717340756</v>
       </c>
       <c r="D65">
-        <v>26432.857474102821</v>
+        <v>11488.700872741154</v>
       </c>
       <c r="E65">
-        <v>26778.795292795556</v>
+        <v>11487.650047520421</v>
       </c>
       <c r="F65">
-        <v>27104.28868653786</v>
+        <v>11472.984368819536</v>
       </c>
       <c r="G65">
-        <v>27430.226791748173</v>
+        <v>11471.694809933386</v>
       </c>
       <c r="H65">
-        <v>27752.148921255517</v>
+        <v>11469.054724813679</v>
       </c>
       <c r="I65">
-        <v>28061.454640667642</v>
+        <v>11460.640697119017</v>
       </c>
       <c r="J65">
-        <v>28360.054332563141</v>
+        <v>11446.434468706462</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C66" s="2">
-        <v>7102.1703459052405</v>
+        <v>26061.852712436965</v>
       </c>
       <c r="D66">
-        <v>7101.9283963126609</v>
+        <v>26432.857474102821</v>
       </c>
       <c r="E66">
-        <v>7103.0352596061684</v>
+        <v>26778.795292795556</v>
       </c>
       <c r="F66">
-        <v>7109.6536369225423</v>
+        <v>27104.28868653786</v>
       </c>
       <c r="G66">
-        <v>7128.7764447610398</v>
+        <v>27430.226791748173</v>
       </c>
       <c r="H66">
-        <v>7148.5724834190496</v>
+        <v>27752.148921255517</v>
       </c>
       <c r="I66">
-        <v>7166.8884379133542</v>
+        <v>28061.454640667642</v>
       </c>
       <c r="J66">
-        <v>7183.5236174847623</v>
+        <v>28360.054332563141</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="2">
-        <v>601</v>
+        <v>511</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C67" s="2">
-        <v>137471.87134663673</v>
+        <v>7102.1703459052405</v>
       </c>
       <c r="D67">
-        <v>138622.1909285344</v>
+        <v>7101.9283963126609</v>
       </c>
       <c r="E67">
-        <v>139669.23476028081</v>
+        <v>7103.0352596061684</v>
       </c>
       <c r="F67">
-        <v>140786.86271880643</v>
+        <v>7109.6536369225423</v>
       </c>
       <c r="G67">
-        <v>142028.31274644478</v>
+        <v>7128.7764447610398</v>
       </c>
       <c r="H67">
-        <v>143233.42003857886</v>
+        <v>7148.5724834190496</v>
       </c>
       <c r="I67">
-        <v>144410.26902367431</v>
+        <v>7166.8884379133542</v>
       </c>
       <c r="J67">
-        <v>145576.23023604468</v>
+        <v>7183.5236174847623</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C68" s="2">
-        <v>33409.314792378209</v>
+        <v>137471.87134663673</v>
       </c>
       <c r="D68">
-        <v>33760.731194531429</v>
+        <v>138622.1909285344</v>
       </c>
       <c r="E68">
-        <v>34092.733596011218</v>
+        <v>139669.23476028081</v>
       </c>
       <c r="F68">
-        <v>34434.907358178658</v>
+        <v>140786.86271880643</v>
       </c>
       <c r="G68">
-        <v>34805.78131311688</v>
+        <v>142028.31274644478</v>
       </c>
       <c r="H68">
-        <v>35161.331032199145</v>
+        <v>143233.42003857886</v>
       </c>
       <c r="I68">
-        <v>35500.510176479496</v>
+        <v>144410.26902367431</v>
       </c>
       <c r="J68">
-        <v>35825.708070505003</v>
+        <v>145576.23023604468</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C69" s="2">
-        <v>52550.463292340683</v>
+        <v>33409.314792378209</v>
       </c>
       <c r="D69">
-        <v>53005.538447166226</v>
+        <v>33760.731194531429</v>
       </c>
       <c r="E69">
-        <v>53411.79684684235</v>
+        <v>34092.733596011218</v>
       </c>
       <c r="F69">
-        <v>53830.81565652453</v>
+        <v>34434.907358178658</v>
       </c>
       <c r="G69">
-        <v>54272.438466294669</v>
+        <v>34805.78131311688</v>
       </c>
       <c r="H69">
-        <v>54690.486192918121</v>
+        <v>35161.331032199145</v>
       </c>
       <c r="I69">
-        <v>55087.875884675537</v>
+        <v>35500.510176479496</v>
       </c>
       <c r="J69">
-        <v>55472.108825667747</v>
+        <v>35825.708070505003</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C70" s="2">
-        <v>14564.88873797431</v>
+        <v>52550.463292340683</v>
       </c>
       <c r="D70">
-        <v>14634.672715063702</v>
+        <v>53005.538447166226</v>
       </c>
       <c r="E70">
-        <v>14690.24025358568</v>
+        <v>53411.79684684235</v>
       </c>
       <c r="F70">
-        <v>14747.701589789698</v>
+        <v>53830.81565652453</v>
       </c>
       <c r="G70">
-        <v>14822.099996719502</v>
+        <v>54272.438466294669</v>
       </c>
       <c r="H70">
-        <v>14894.357629431066</v>
+        <v>54690.486192918121</v>
       </c>
       <c r="I70">
-        <v>14962.751737423665</v>
+        <v>55087.875884675537</v>
       </c>
       <c r="J70">
-        <v>15028.522789483945</v>
+        <v>55472.108825667747</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C71" s="2">
-        <v>29567.044098543542</v>
+        <v>14564.88873797431</v>
       </c>
       <c r="D71">
-        <v>29568.130873632945</v>
+        <v>14634.672715063702</v>
       </c>
       <c r="E71">
-        <v>29539.720646424161</v>
+        <v>14690.24025358568</v>
       </c>
       <c r="F71">
-        <v>29513.238706200078</v>
+        <v>14747.701589789698</v>
       </c>
       <c r="G71">
-        <v>29509.975556302401</v>
+        <v>14822.099996719502</v>
       </c>
       <c r="H71">
-        <v>29494.738977265297</v>
+        <v>14894.357629431066</v>
       </c>
       <c r="I71">
-        <v>29465.672706830199</v>
+        <v>14962.751737423665</v>
       </c>
       <c r="J71">
-        <v>29425.737011721303</v>
+        <v>15028.522789483945</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C72" s="2">
-        <v>33050.969850982001</v>
+        <v>29567.044098543542</v>
       </c>
       <c r="D72">
-        <v>33398.187405001925</v>
+        <v>29568.130873632945</v>
       </c>
       <c r="E72">
-        <v>33715.629694663803</v>
+        <v>29539.720646424161</v>
       </c>
       <c r="F72">
-        <v>34038.693544492795</v>
+        <v>29513.238706200078</v>
       </c>
       <c r="G72">
-        <v>34380.63407277529</v>
+        <v>29509.975556302401</v>
       </c>
       <c r="H72">
-        <v>34707.091582657289</v>
+        <v>29494.738977265297</v>
       </c>
       <c r="I72">
-        <v>35020.2303525475</v>
+        <v>29465.672706830199</v>
       </c>
       <c r="J72">
-        <v>35323.581884937594</v>
+        <v>29425.737011721303</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C73" s="2">
-        <v>32039.288694175266</v>
+        <v>33050.969850982001</v>
       </c>
       <c r="D73">
-        <v>32055.881805403784</v>
+        <v>33398.187405001925</v>
       </c>
       <c r="E73">
-        <v>32038.24416460286</v>
+        <v>33715.629694663803</v>
       </c>
       <c r="F73">
-        <v>32024.754160552184</v>
+        <v>34038.693544492795</v>
       </c>
       <c r="G73">
-        <v>32030.070823443006</v>
+        <v>34380.63407277529</v>
       </c>
       <c r="H73">
-        <v>32017.867512120571</v>
+        <v>34707.091582657289</v>
       </c>
       <c r="I73">
-        <v>31989.219610825563</v>
+        <v>35020.2303525475</v>
       </c>
       <c r="J73">
-        <v>31948.939310606867</v>
+        <v>35323.581884937594</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C74" s="2">
-        <v>36461.088623227894</v>
+        <v>32039.288694175266</v>
       </c>
       <c r="D74">
-        <v>36336.848304907893</v>
+        <v>32055.881805403784</v>
       </c>
       <c r="E74">
-        <v>36184.950095329274</v>
+        <v>32038.24416460286</v>
       </c>
       <c r="F74">
-        <v>36041.362555985899</v>
+        <v>32024.754160552184</v>
       </c>
       <c r="G74">
-        <v>35915.209300255723</v>
+        <v>32030.070823443006</v>
       </c>
       <c r="H74">
-        <v>35761.992411088126</v>
+        <v>32017.867512120571</v>
       </c>
       <c r="I74">
-        <v>35581.922363362595</v>
+        <v>31989.219610825563</v>
       </c>
       <c r="J74">
-        <v>35378.97005636117</v>
+        <v>31948.939310606867</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C75" s="2">
-        <v>20834.340359595444</v>
+        <v>36461.088623227894</v>
       </c>
       <c r="D75">
-        <v>21118.325291034198</v>
+        <v>36336.848304907893</v>
       </c>
       <c r="E75">
-        <v>21386.968566151347</v>
+        <v>36184.950095329274</v>
       </c>
       <c r="F75">
-        <v>21666.538822265844</v>
+        <v>36041.362555985899</v>
       </c>
       <c r="G75">
-        <v>21961.277701363386</v>
+        <v>35915.209300255723</v>
       </c>
       <c r="H75">
-        <v>22249.916373978627</v>
+        <v>35761.992411088126</v>
       </c>
       <c r="I75">
-        <v>22534.501356755576</v>
+        <v>35581.922363362595</v>
       </c>
       <c r="J75">
-        <v>22817.927866270715</v>
+        <v>35378.97005636117</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C76" s="2">
-        <v>51926.454889730572</v>
+        <v>20834.340359595444</v>
       </c>
       <c r="D76">
-        <v>52199.58449814147</v>
+        <v>21118.325291034198</v>
       </c>
       <c r="E76">
-        <v>52421.173626822027</v>
+        <v>21386.968566151347</v>
       </c>
       <c r="F76">
-        <v>52655.591317680693</v>
+        <v>21666.538822265844</v>
       </c>
       <c r="G76">
-        <v>52917.543057532093</v>
+        <v>21961.277701363386</v>
       </c>
       <c r="H76">
-        <v>53152.883404869281</v>
+        <v>22249.916373978627</v>
       </c>
       <c r="I76">
-        <v>53364.746085284474</v>
+        <v>22534.501356755576</v>
       </c>
       <c r="J76">
-        <v>53558.785035334222</v>
+        <v>22817.927866270715</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C77" s="2">
-        <v>25410.003899916341</v>
+        <v>51926.454889730572</v>
       </c>
       <c r="D77">
-        <v>25995.27212760433</v>
+        <v>52199.58449814147</v>
       </c>
       <c r="E77">
-        <v>26563.983432933936</v>
+        <v>52421.173626822027</v>
       </c>
       <c r="F77">
-        <v>27138.561757265612</v>
+        <v>52655.591317680693</v>
       </c>
       <c r="G77">
-        <v>27722.698134071688</v>
+        <v>52917.543057532093</v>
       </c>
       <c r="H77">
-        <v>28298.222841163813</v>
+        <v>53152.883404869281</v>
       </c>
       <c r="I77">
-        <v>28866.258284091902</v>
+        <v>53364.746085284474</v>
       </c>
       <c r="J77">
-        <v>29429.547626980395</v>
+        <v>53558.785035334222</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C78" s="2">
-        <v>4723.7495104457066</v>
+        <v>25410.003899916341</v>
       </c>
       <c r="D78">
-        <v>4749.5531303392127</v>
+        <v>25995.27212760433</v>
       </c>
       <c r="E78">
-        <v>4769.2900466248302</v>
+        <v>26563.983432933936</v>
       </c>
       <c r="F78">
-        <v>4788.0110649153085</v>
+        <v>27138.561757265612</v>
       </c>
       <c r="G78">
-        <v>4808.7186334205744</v>
+        <v>27722.698134071688</v>
       </c>
       <c r="H78">
-        <v>4827.3312634058002</v>
+        <v>28298.222841163813</v>
       </c>
       <c r="I78">
-        <v>4843.7572646564395</v>
+        <v>28866.258284091902</v>
       </c>
       <c r="J78">
-        <v>4858.5389690698266</v>
+        <v>29429.547626980395</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C79" s="2">
-        <v>12532.241626081443</v>
+        <v>4723.7495104457066</v>
       </c>
       <c r="D79">
-        <v>12785.831638954771</v>
+        <v>4749.5531303392127</v>
       </c>
       <c r="E79">
-        <v>13026.70706605029</v>
+        <v>4769.2900466248302</v>
       </c>
       <c r="F79">
-        <v>13268.504286378291</v>
+        <v>4788.0110649153085</v>
       </c>
       <c r="G79">
-        <v>13518.082172408282</v>
+        <v>4808.7186334205744</v>
       </c>
       <c r="H79">
-        <v>13765.299521653407</v>
+        <v>4827.3312634058002</v>
       </c>
       <c r="I79">
-        <v>14009.338157462686</v>
+        <v>4843.7572646564395</v>
       </c>
       <c r="J79">
-        <v>14251.666326400835</v>
+        <v>4858.5389690698266</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="2">
-        <v>701</v>
+        <v>613</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C80" s="2">
-        <v>93441.203508879888</v>
+        <v>12532.241626081443</v>
       </c>
       <c r="D80">
-        <v>93260.836669515818</v>
+        <v>12785.831638954771</v>
       </c>
       <c r="E80">
-        <v>92993.180965096079</v>
+        <v>13026.70706605029</v>
       </c>
       <c r="F80">
-        <v>92745.867443255062</v>
+        <v>13268.504286378291</v>
       </c>
       <c r="G80">
-        <v>92558.711317772249</v>
+        <v>13518.082172408282</v>
       </c>
       <c r="H80">
-        <v>92328.202832339302</v>
+        <v>13765.299521653407</v>
       </c>
       <c r="I80">
-        <v>92064.490511855663</v>
+        <v>14009.338157462686</v>
       </c>
       <c r="J80">
-        <v>91782.496374190567</v>
+        <v>14251.666326400835</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C81" s="2">
-        <v>148901.97962131642</v>
+        <v>93441.203508879888</v>
       </c>
       <c r="D81">
-        <v>150233.71599701775</v>
+        <v>93260.836669515818</v>
       </c>
       <c r="E81">
-        <v>151418.55862790885</v>
+        <v>92993.180965096079</v>
       </c>
       <c r="F81">
-        <v>152626.11389307617</v>
+        <v>92745.867443255062</v>
       </c>
       <c r="G81">
-        <v>153892.11351639888</v>
+        <v>92558.711317772249</v>
       </c>
       <c r="H81">
-        <v>155073.82604137395</v>
+        <v>92328.202832339302</v>
       </c>
       <c r="I81">
-        <v>156180.63704778673</v>
+        <v>92064.490511855663</v>
       </c>
       <c r="J81">
-        <v>157231.68724453964</v>
+        <v>91782.496374190567</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C82" s="2">
-        <v>56935.574463207653</v>
+        <v>148901.97962131642</v>
       </c>
       <c r="D82">
-        <v>56901.64868254523</v>
+        <v>150233.71599701775</v>
       </c>
       <c r="E82">
-        <v>56874.570231878577</v>
+        <v>151418.55862790885</v>
       </c>
       <c r="F82">
-        <v>56902.662731546385</v>
+        <v>152626.11389307617</v>
       </c>
       <c r="G82">
-        <v>56986.093408844419</v>
+        <v>153892.11351639888</v>
       </c>
       <c r="H82">
-        <v>57058.749044344971</v>
+        <v>155073.82604137395</v>
       </c>
       <c r="I82">
-        <v>57115.941284613567</v>
+        <v>156180.63704778673</v>
       </c>
       <c r="J82">
-        <v>57158.03830536145</v>
+        <v>157231.68724453964</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83" s="2">
-        <v>42872.750282955603</v>
+        <v>56935.574463207653</v>
       </c>
       <c r="D83">
-        <v>43442.688018546309</v>
+        <v>56901.64868254523</v>
       </c>
       <c r="E83">
-        <v>43972.932569263918</v>
+        <v>56874.570231878577</v>
       </c>
       <c r="F83">
-        <v>44510.532030698756</v>
+        <v>56902.662731546385</v>
       </c>
       <c r="G83">
-        <v>45061.872726953341</v>
+        <v>56986.093408844419</v>
       </c>
       <c r="H83">
-        <v>45601.19856147925</v>
+        <v>57058.749044344971</v>
       </c>
       <c r="I83">
-        <v>46130.249266255123</v>
+        <v>57115.941284613567</v>
       </c>
       <c r="J83">
-        <v>46657.133347646988</v>
+        <v>57158.03830536145</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="2">
+        <v>704</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C84" s="2">
+        <v>42872.750282955603</v>
+      </c>
+      <c r="D84">
+        <v>43442.688018546309</v>
+      </c>
+      <c r="E84">
+        <v>43972.932569263918</v>
+      </c>
+      <c r="F84">
+        <v>44510.532030698756</v>
+      </c>
+      <c r="G84">
+        <v>45061.872726953341</v>
+      </c>
+      <c r="H84">
+        <v>45601.19856147925</v>
+      </c>
+      <c r="I84">
+        <v>46130.249266255123</v>
+      </c>
+      <c r="J84">
+        <v>46657.133347646988</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="2">
         <v>705</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C85" s="2">
         <v>44129.391173650161</v>
       </c>
-      <c r="D84">
+      <c r="D85">
         <v>44393.880123102412</v>
       </c>
-      <c r="E84">
+      <c r="E85">
         <v>44615.106843880349</v>
       </c>
-      <c r="F84">
+      <c r="F85">
         <v>44841.149898891672</v>
       </c>
-      <c r="G84">
+      <c r="G85">
         <v>45076.478621960821</v>
       </c>
-      <c r="H84">
+      <c r="H85">
         <v>45291.400921535038</v>
       </c>
-      <c r="I84">
+      <c r="I85">
         <v>45488.036684274666</v>
       </c>
-      <c r="J84">
+      <c r="J85">
         <v>45673.211079207387</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
-      <c r="A85" s="3">
+    <row r="86" spans="1:10">
+      <c r="A86" s="3">
         <v>706</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B86" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C85" s="2">
+      <c r="C86" s="2">
         <v>55137.943035120479</v>
       </c>
-      <c r="D85">
+      <c r="D86">
         <v>55805.177069790196</v>
       </c>
-      <c r="E85">
+      <c r="E86">
         <v>56410.736435833067</v>
       </c>
-      <c r="F85">
+      <c r="F86">
         <v>57019.167947271082</v>
       </c>
-      <c r="G85">
+      <c r="G86">
         <v>57646.345716059077</v>
       </c>
-      <c r="H85">
+      <c r="H86">
         <v>58247.048755960444</v>
       </c>
-      <c r="I85">
+      <c r="I86">
         <v>58822.220126410779</v>
       </c>
-      <c r="J85">
+      <c r="J86">
         <v>59380.094479342159</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
-      <c r="A86" s="5">
-        <v>0</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C86">
-        <f>SUM(C2:C85)</f>
-        <v>5020970.0892126299</v>
-      </c>
-      <c r="D86">
-        <f t="shared" ref="D86:J86" si="0">SUM(D2:D85)</f>
-        <v>5051379.2310498413</v>
-      </c>
-      <c r="E86">
-        <f t="shared" si="0"/>
-        <v>5077666.8598168911</v>
-      </c>
-      <c r="F86">
-        <f t="shared" si="0"/>
-        <v>5104906.8366506081</v>
-      </c>
-      <c r="G86">
-        <f t="shared" si="0"/>
-        <v>5135911.6221289076</v>
-      </c>
-      <c r="H86">
-        <f t="shared" si="0"/>
-        <v>5164859.9393230798</v>
-      </c>
-      <c r="I86">
-        <f t="shared" si="0"/>
-        <v>5191823.0799561189</v>
-      </c>
-      <c r="J86">
-        <f t="shared" si="0"/>
-        <v>5217294.9784566956</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3500,19 +4397,19 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2">
-        <v>101</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>93</v>
       </c>
       <c r="C2">
         <f>((anual!I2-anual!D2)/7)/anual!D2</f>
-        <v>1.868100218500498E-3</v>
+        <v>3.9718671018175106E-3</v>
       </c>
       <c r="D2">
         <f>anual!C2</f>
-        <v>347692.45856501424</v>
+        <v>5020970.0892126299</v>
       </c>
       <c r="E2" s="4">
         <f>5/53</f>
@@ -3521,18 +4418,18 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <f>((anual!I3-anual!D3)/7)/anual!D3</f>
-        <v>3.1527798760231261E-3</v>
+        <v>1.868100218500498E-3</v>
       </c>
       <c r="D3">
         <f>anual!C3</f>
-        <v>69342.771863127593</v>
+        <v>347692.45856501424</v>
       </c>
       <c r="E3" s="4">
         <f>5/53</f>
@@ -3541,58 +4438,58 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <f>((anual!I4-anual!D4)/7)/anual!D4</f>
-        <v>3.087060729904154E-3</v>
+        <v>3.1527798760231261E-3</v>
       </c>
       <c r="D4">
         <f>anual!C4</f>
-        <v>238762.28232309327</v>
+        <v>69342.771863127593</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" ref="E4:E67" si="0">5/53</f>
+        <f>5/53</f>
         <v>9.4339622641509441E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <f>((anual!I5-anual!D5)/7)/anual!D5</f>
-        <v>2.9674075772079603E-3</v>
+        <v>3.087060729904154E-3</v>
       </c>
       <c r="D5">
         <f>anual!C5</f>
-        <v>38240.587050800503</v>
+        <v>238762.28232309327</v>
       </c>
       <c r="E5" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E5:E68" si="0">5/53</f>
         <v>9.4339622641509441E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <f>((anual!I6-anual!D6)/7)/anual!D6</f>
-        <v>1.0804017806949633E-3</v>
+        <v>2.9674075772079603E-3</v>
       </c>
       <c r="D6">
         <f>anual!C6</f>
-        <v>17842.632764587546</v>
+        <v>38240.587050800503</v>
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
@@ -3601,18 +4498,18 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <f>((anual!I7-anual!D7)/7)/anual!D7</f>
-        <v>2.2427367342404908E-3</v>
+        <v>1.0804017806949633E-3</v>
       </c>
       <c r="D7">
         <f>anual!C7</f>
-        <v>61640.79175785082</v>
+        <v>17842.632764587546</v>
       </c>
       <c r="E7" s="4">
         <f t="shared" si="0"/>
@@ -3621,18 +4518,18 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <f>((anual!I8-anual!D8)/7)/anual!D8</f>
-        <v>2.0638506204688394E-3</v>
+        <v>2.2427367342404908E-3</v>
       </c>
       <c r="D8">
         <f>anual!C8</f>
-        <v>28301.543605497558</v>
+        <v>61640.79175785082</v>
       </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
@@ -3641,18 +4538,18 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <f>((anual!I9-anual!D9)/7)/anual!D9</f>
-        <v>2.5998944003007085E-3</v>
+        <v>2.0638506204688394E-3</v>
       </c>
       <c r="D9">
         <f>anual!C9</f>
-        <v>137108.97722321076</v>
+        <v>28301.543605497558</v>
       </c>
       <c r="E9" s="4">
         <f t="shared" si="0"/>
@@ -3661,18 +4558,18 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <f>((anual!I10-anual!D10)/7)/anual!D10</f>
-        <v>5.5331855705229279E-3</v>
+        <v>2.5998944003007085E-3</v>
       </c>
       <c r="D10">
         <f>anual!C10</f>
-        <v>59327.717623552853</v>
+        <v>137108.97722321076</v>
       </c>
       <c r="E10" s="4">
         <f t="shared" si="0"/>
@@ -3681,18 +4578,18 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11">
         <f>((anual!I11-anual!D11)/7)/anual!D11</f>
-        <v>6.0189412595965733E-3</v>
+        <v>5.5331855705229279E-3</v>
       </c>
       <c r="D11">
         <f>anual!C11</f>
-        <v>92686.07744882835</v>
+        <v>59327.717623552853</v>
       </c>
       <c r="E11" s="4">
         <f t="shared" si="0"/>
@@ -3701,18 +4598,18 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <f>((anual!I12-anual!D12)/7)/anual!D12</f>
-        <v>3.7542523553232084E-3</v>
+        <v>6.0189412595965733E-3</v>
       </c>
       <c r="D12">
         <f>anual!C12</f>
-        <v>69754.925417826904</v>
+        <v>92686.07744882835</v>
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
@@ -3721,18 +4618,18 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13">
         <f>((anual!I13-anual!D13)/7)/anual!D13</f>
-        <v>1.5256857218822817E-3</v>
+        <v>3.7542523553232084E-3</v>
       </c>
       <c r="D13">
         <f>anual!C13</f>
-        <v>21699.266475138473</v>
+        <v>69754.925417826904</v>
       </c>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
@@ -3741,18 +4638,18 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14">
         <f>((anual!I14-anual!D14)/7)/anual!D14</f>
-        <v>2.3705404429928863E-3</v>
+        <v>1.5256857218822817E-3</v>
       </c>
       <c r="D14">
         <f>anual!C14</f>
-        <v>83692.119332512375</v>
+        <v>21699.266475138473</v>
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
@@ -3761,18 +4658,18 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15">
         <f>((anual!I15-anual!D15)/7)/anual!D15</f>
-        <v>9.4827452934470851E-4</v>
+        <v>2.3705404429928863E-3</v>
       </c>
       <c r="D15">
         <f>anual!C15</f>
-        <v>61121.852323967265</v>
+        <v>83692.119332512375</v>
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
@@ -3781,18 +4678,18 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16">
         <f>((anual!I16-anual!D16)/7)/anual!D16</f>
-        <v>-5.3284409479437069E-4</v>
+        <v>9.4827452934470851E-4</v>
       </c>
       <c r="D16">
         <f>anual!C16</f>
-        <v>61401.434959428974</v>
+        <v>61121.852323967265</v>
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
@@ -3801,18 +4698,18 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17">
         <f>((anual!I17-anual!D17)/7)/anual!D17</f>
-        <v>4.5148043493114355E-3</v>
+        <v>-5.3284409479437069E-4</v>
       </c>
       <c r="D17">
         <f>anual!C17</f>
-        <v>7122.4202578776185</v>
+        <v>61401.434959428974</v>
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
@@ -3821,18 +4718,18 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18">
         <f>((anual!I18-anual!D18)/7)/anual!D18</f>
-        <v>5.9882081108790237E-4</v>
+        <v>4.5148043493114355E-3</v>
       </c>
       <c r="D18">
         <f>anual!C18</f>
-        <v>7759.3518669735276</v>
+        <v>7122.4202578776185</v>
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
@@ -3841,18 +4738,18 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19">
         <f>((anual!I19-anual!D19)/7)/anual!D19</f>
-        <v>2.0284040722509987E-3</v>
+        <v>5.9882081108790237E-4</v>
       </c>
       <c r="D19">
         <f>anual!C19</f>
-        <v>78069.636218031286</v>
+        <v>7759.3518669735276</v>
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
@@ -3861,18 +4758,18 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20">
         <f>((anual!I20-anual!D20)/7)/anual!D20</f>
-        <v>-1.8406580355975945E-3</v>
+        <v>2.0284040722509987E-3</v>
       </c>
       <c r="D20">
         <f>anual!C20</f>
-        <v>135629.67197663515</v>
+        <v>78069.636218031286</v>
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
@@ -3881,18 +4778,18 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <f>((anual!I21-anual!D21)/7)/anual!D21</f>
-        <v>3.4707894205274446E-3</v>
+        <v>-1.8406580355975945E-3</v>
       </c>
       <c r="D21">
         <f>anual!C21</f>
-        <v>13110.005500423718</v>
+        <v>135629.67197663515</v>
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
@@ -3901,18 +4798,18 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22">
         <f>((anual!I22-anual!D22)/7)/anual!D22</f>
-        <v>5.4598986657930669E-3</v>
+        <v>3.4707894205274446E-3</v>
       </c>
       <c r="D22">
         <f>anual!C22</f>
-        <v>313360.92561695981</v>
+        <v>13110.005500423718</v>
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
@@ -3921,18 +4818,18 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23">
         <f>((anual!I23-anual!D23)/7)/anual!D23</f>
-        <v>4.3743395004128211E-3</v>
+        <v>5.4598986657930669E-3</v>
       </c>
       <c r="D23">
         <f>anual!C23</f>
-        <v>89238.4691379383</v>
+        <v>313360.92561695981</v>
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
@@ -3941,18 +4838,18 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24">
         <f>((anual!I24-anual!D24)/7)/anual!D24</f>
-        <v>4.5811336827644303E-3</v>
+        <v>4.3743395004128211E-3</v>
       </c>
       <c r="D24">
         <f>anual!C24</f>
-        <v>77877.077161967609</v>
+        <v>89238.4691379383</v>
       </c>
       <c r="E24" s="4">
         <f t="shared" si="0"/>
@@ -3961,18 +4858,18 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25">
         <f>((anual!I25-anual!D25)/7)/anual!D25</f>
-        <v>3.5509672576142549E-3</v>
+        <v>4.5811336827644303E-3</v>
       </c>
       <c r="D25">
         <f>anual!C25</f>
-        <v>7320.929017146681</v>
+        <v>77877.077161967609</v>
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
@@ -3981,18 +4878,18 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26">
         <f>((anual!I26-anual!D26)/7)/anual!D26</f>
-        <v>3.9986888451666348E-3</v>
+        <v>3.5509672576142549E-3</v>
       </c>
       <c r="D26">
         <f>anual!C26</f>
-        <v>29541.082982532505</v>
+        <v>7320.929017146681</v>
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
@@ -4001,18 +4898,18 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27">
         <f>((anual!I27-anual!D27)/7)/anual!D27</f>
-        <v>3.812647734999011E-3</v>
+        <v>3.9986888451666348E-3</v>
       </c>
       <c r="D27">
         <f>anual!C27</f>
-        <v>48765.107980937304</v>
+        <v>29541.082982532505</v>
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
@@ -4021,18 +4918,18 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28">
         <f>((anual!I28-anual!D28)/7)/anual!D28</f>
-        <v>5.0224082644080353E-3</v>
+        <v>3.812647734999011E-3</v>
       </c>
       <c r="D28">
         <f>anual!C28</f>
-        <v>40963.256483213729</v>
+        <v>48765.107980937304</v>
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
@@ -4041,18 +4938,18 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29">
         <f>((anual!I29-anual!D29)/7)/anual!D29</f>
-        <v>5.9951805849104709E-3</v>
+        <v>5.0224082644080353E-3</v>
       </c>
       <c r="D29">
         <f>anual!C29</f>
-        <v>33882.600982043499</v>
+        <v>40963.256483213729</v>
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
@@ -4061,18 +4958,18 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30">
         <f>((anual!I30-anual!D30)/7)/anual!D30</f>
-        <v>6.5649523334877563E-3</v>
+        <v>5.9951805849104709E-3</v>
       </c>
       <c r="D30">
         <f>anual!C30</f>
-        <v>23883.945695728271</v>
+        <v>33882.600982043499</v>
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
@@ -4081,18 +4978,18 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31">
         <f>((anual!I31-anual!D31)/7)/anual!D31</f>
-        <v>6.5438608113860194E-3</v>
+        <v>6.5649523334877563E-3</v>
       </c>
       <c r="D31">
         <f>anual!C31</f>
-        <v>200446.33903553456</v>
+        <v>23883.945695728271</v>
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
@@ -4101,18 +4998,18 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32">
         <f>((anual!I32-anual!D32)/7)/anual!D32</f>
-        <v>3.4531094457913684E-3</v>
+        <v>6.5438608113860194E-3</v>
       </c>
       <c r="D32">
         <f>anual!C32</f>
-        <v>14410.500892204112</v>
+        <v>200446.33903553456</v>
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
@@ -4121,18 +5018,18 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33">
         <f>((anual!I33-anual!D33)/7)/anual!D33</f>
-        <v>3.5841874694335094E-3</v>
+        <v>3.4531094457913684E-3</v>
       </c>
       <c r="D33">
         <f>anual!C33</f>
-        <v>22165.483844052134</v>
+        <v>14410.500892204112</v>
       </c>
       <c r="E33" s="4">
         <f t="shared" si="0"/>
@@ -4141,18 +5038,18 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34">
         <f>((anual!I34-anual!D34)/7)/anual!D34</f>
-        <v>5.3724116208518939E-3</v>
+        <v>3.5841874694335094E-3</v>
       </c>
       <c r="D34">
         <f>anual!C34</f>
-        <v>54442.633617922635</v>
+        <v>22165.483844052134</v>
       </c>
       <c r="E34" s="4">
         <f t="shared" si="0"/>
@@ -4161,18 +5058,18 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35">
         <f>((anual!I35-anual!D35)/7)/anual!D35</f>
-        <v>1.1409413530946664E-2</v>
+        <v>5.3724116208518939E-3</v>
       </c>
       <c r="D35">
         <f>anual!C35</f>
-        <v>34045.178955669733</v>
+        <v>54442.633617922635</v>
       </c>
       <c r="E35" s="4">
         <f t="shared" si="0"/>
@@ -4181,18 +5078,18 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36">
         <f>((anual!I36-anual!D36)/7)/anual!D36</f>
-        <v>4.9476740207180722E-3</v>
+        <v>1.1409413530946664E-2</v>
       </c>
       <c r="D36">
         <f>anual!C36</f>
-        <v>19166.649236339777</v>
+        <v>34045.178955669733</v>
       </c>
       <c r="E36" s="4">
         <f t="shared" si="0"/>
@@ -4201,18 +5098,18 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C37">
         <f>((anual!I37-anual!D37)/7)/anual!D37</f>
-        <v>1.0201788943689527E-2</v>
+        <v>4.9476740207180722E-3</v>
       </c>
       <c r="D37">
         <f>anual!C37</f>
-        <v>16589.593831471066</v>
+        <v>19166.649236339777</v>
       </c>
       <c r="E37" s="4">
         <f t="shared" si="0"/>
@@ -4221,18 +5118,18 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>301</v>
+        <v>216</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C38">
         <f>((anual!I38-anual!D38)/7)/anual!D38</f>
-        <v>1.7631233970079299E-3</v>
+        <v>1.0201788943689527E-2</v>
       </c>
       <c r="D38">
         <f>anual!C38</f>
-        <v>160800.54777507891</v>
+        <v>16589.593831471066</v>
       </c>
       <c r="E38" s="4">
         <f t="shared" si="0"/>
@@ -4241,18 +5138,18 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39">
         <f>((anual!I39-anual!D39)/7)/anual!D39</f>
-        <v>1.9409233851842747E-3</v>
+        <v>1.7631233970079299E-3</v>
       </c>
       <c r="D39">
         <f>anual!C39</f>
-        <v>60503.614472114554</v>
+        <v>160800.54777507891</v>
       </c>
       <c r="E39" s="4">
         <f t="shared" si="0"/>
@@ -4261,18 +5158,18 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C40">
         <f>((anual!I40-anual!D40)/7)/anual!D40</f>
-        <v>3.2813645124535793E-3</v>
+        <v>1.9409233851842747E-3</v>
       </c>
       <c r="D40">
         <f>anual!C40</f>
-        <v>111181.99268416413</v>
+        <v>60503.614472114554</v>
       </c>
       <c r="E40" s="4">
         <f t="shared" si="0"/>
@@ -4281,18 +5178,18 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41">
         <f>((anual!I41-anual!D41)/7)/anual!D41</f>
-        <v>-1.875319691834949E-3</v>
+        <v>3.2813645124535793E-3</v>
       </c>
       <c r="D41">
         <f>anual!C41</f>
-        <v>16013.572967355041</v>
+        <v>111181.99268416413</v>
       </c>
       <c r="E41" s="4">
         <f t="shared" si="0"/>
@@ -4301,18 +5198,18 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C42">
         <f>((anual!I42-anual!D42)/7)/anual!D42</f>
-        <v>-2.8414147425063594E-3</v>
+        <v>-1.875319691834949E-3</v>
       </c>
       <c r="D42">
         <f>anual!C42</f>
-        <v>70325.525267318735</v>
+        <v>16013.572967355041</v>
       </c>
       <c r="E42" s="4">
         <f t="shared" si="0"/>
@@ -4321,18 +5218,18 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C43">
         <f>((anual!I43-anual!D43)/7)/anual!D43</f>
-        <v>1.027499633523098E-3</v>
+        <v>-2.8414147425063594E-3</v>
       </c>
       <c r="D43">
         <f>anual!C43</f>
-        <v>15059.088779095084</v>
+        <v>70325.525267318735</v>
       </c>
       <c r="E43" s="4">
         <f t="shared" si="0"/>
@@ -4341,18 +5238,18 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44">
         <f>((anual!I44-anual!D44)/7)/anual!D44</f>
-        <v>1.586539610801402E-3</v>
+        <v>1.027499633523098E-3</v>
       </c>
       <c r="D44">
         <f>anual!C44</f>
-        <v>48159.580867468983</v>
+        <v>15059.088779095084</v>
       </c>
       <c r="E44" s="4">
         <f t="shared" si="0"/>
@@ -4361,18 +5258,18 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45">
         <f>((anual!I45-anual!D45)/7)/anual!D45</f>
-        <v>1.9796925213435004E-3</v>
+        <v>1.586539610801402E-3</v>
       </c>
       <c r="D45">
         <f>anual!C45</f>
-        <v>44512.114468701118</v>
+        <v>48159.580867468983</v>
       </c>
       <c r="E45" s="4">
         <f t="shared" si="0"/>
@@ -4381,18 +5278,18 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>401</v>
+        <v>308</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46">
         <f>((anual!I46-anual!D46)/7)/anual!D46</f>
-        <v>4.417625643832134E-3</v>
+        <v>1.9796925213435004E-3</v>
       </c>
       <c r="D46">
         <f>anual!C46</f>
-        <v>141279.33236905705</v>
+        <v>44512.114468701118</v>
       </c>
       <c r="E46" s="4">
         <f t="shared" si="0"/>
@@ -4401,18 +5298,18 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C47">
         <f>((anual!I47-anual!D47)/7)/anual!D47</f>
-        <v>6.1172090172660109E-3</v>
+        <v>4.417625643832134E-3</v>
       </c>
       <c r="D47">
         <f>anual!C47</f>
-        <v>46412.577574639348</v>
+        <v>141279.33236905705</v>
       </c>
       <c r="E47" s="4">
         <f t="shared" si="0"/>
@@ -4421,18 +5318,18 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48">
         <f>((anual!I48-anual!D48)/7)/anual!D48</f>
-        <v>3.3805719623731241E-3</v>
+        <v>6.1172090172660109E-3</v>
       </c>
       <c r="D48">
         <f>anual!C48</f>
-        <v>48618.467107528188</v>
+        <v>46412.577574639348</v>
       </c>
       <c r="E48" s="4">
         <f t="shared" si="0"/>
@@ -4441,18 +5338,18 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49">
         <f>((anual!I49-anual!D49)/7)/anual!D49</f>
-        <v>5.7772007659230677E-3</v>
+        <v>3.3805719623731241E-3</v>
       </c>
       <c r="D49">
         <f>anual!C49</f>
-        <v>42982.873210465354</v>
+        <v>48618.467107528188</v>
       </c>
       <c r="E49" s="4">
         <f t="shared" si="0"/>
@@ -4461,18 +5358,18 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C50">
         <f>((anual!I50-anual!D50)/7)/anual!D50</f>
-        <v>5.2870262626682684E-3</v>
+        <v>5.7772007659230677E-3</v>
       </c>
       <c r="D50">
         <f>anual!C50</f>
-        <v>54313.580033103179</v>
+        <v>42982.873210465354</v>
       </c>
       <c r="E50" s="4">
         <f t="shared" si="0"/>
@@ -4481,18 +5378,18 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C51">
         <f>((anual!I51-anual!D51)/7)/anual!D51</f>
-        <v>3.7952413768835049E-3</v>
+        <v>5.2870262626682684E-3</v>
       </c>
       <c r="D51">
         <f>anual!C51</f>
-        <v>22740.240755341045</v>
+        <v>54313.580033103179</v>
       </c>
       <c r="E51" s="4">
         <f t="shared" si="0"/>
@@ -4501,18 +5398,18 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C52">
         <f>((anual!I52-anual!D52)/7)/anual!D52</f>
-        <v>3.115418895730318E-3</v>
+        <v>3.7952413768835049E-3</v>
       </c>
       <c r="D52">
         <f>anual!C52</f>
-        <v>25802.988492663877</v>
+        <v>22740.240755341045</v>
       </c>
       <c r="E52" s="4">
         <f t="shared" si="0"/>
@@ -4521,18 +5418,18 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C53">
         <f>((anual!I53-anual!D53)/7)/anual!D53</f>
-        <v>5.2621279143333392E-3</v>
+        <v>3.115418895730318E-3</v>
       </c>
       <c r="D53">
         <f>anual!C53</f>
-        <v>21193.070036267593</v>
+        <v>25802.988492663877</v>
       </c>
       <c r="E53" s="4">
         <f t="shared" si="0"/>
@@ -4541,18 +5438,18 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C54">
         <f>((anual!I54-anual!D54)/7)/anual!D54</f>
-        <v>1.2046976212780362E-3</v>
+        <v>5.2621279143333392E-3</v>
       </c>
       <c r="D54">
         <f>anual!C54</f>
-        <v>30125.956695576082</v>
+        <v>21193.070036267593</v>
       </c>
       <c r="E54" s="4">
         <f t="shared" si="0"/>
@@ -4561,18 +5458,18 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C55">
         <f>((anual!I55-anual!D55)/7)/anual!D55</f>
-        <v>1.4048524325157918E-2</v>
+        <v>1.2046976212780362E-3</v>
       </c>
       <c r="D55">
         <f>anual!C55</f>
-        <v>86102.105355116975</v>
+        <v>30125.956695576082</v>
       </c>
       <c r="E55" s="4">
         <f t="shared" si="0"/>
@@ -4581,18 +5478,18 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>501</v>
+        <v>410</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C56">
         <f>((anual!I56-anual!D56)/7)/anual!D56</f>
-        <v>8.5168759246700143E-3</v>
+        <v>1.4048524325157918E-2</v>
       </c>
       <c r="D56">
         <f>anual!C56</f>
-        <v>76113.681382974697</v>
+        <v>86102.105355116975</v>
       </c>
       <c r="E56" s="4">
         <f t="shared" si="0"/>
@@ -4601,18 +5498,18 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C57">
         <f>((anual!I57-anual!D57)/7)/anual!D57</f>
-        <v>3.6837367636312524E-3</v>
+        <v>8.5168759246700143E-3</v>
       </c>
       <c r="D57">
         <f>anual!C57</f>
-        <v>57161.818517786087</v>
+        <v>76113.681382974697</v>
       </c>
       <c r="E57" s="4">
         <f t="shared" si="0"/>
@@ -4621,18 +5518,18 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C58">
         <f>((anual!I58-anual!D58)/7)/anual!D58</f>
-        <v>8.479829388756556E-3</v>
+        <v>3.6837367636312524E-3</v>
       </c>
       <c r="D58">
         <f>anual!C58</f>
-        <v>68302.663687150722</v>
+        <v>57161.818517786087</v>
       </c>
       <c r="E58" s="4">
         <f t="shared" si="0"/>
@@ -4641,18 +5538,18 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C59">
         <f>((anual!I59-anual!D59)/7)/anual!D59</f>
-        <v>6.8107718797761913E-3</v>
+        <v>8.479829388756556E-3</v>
       </c>
       <c r="D59">
         <f>anual!C59</f>
-        <v>24209.971915413378</v>
+        <v>68302.663687150722</v>
       </c>
       <c r="E59" s="4">
         <f t="shared" si="0"/>
@@ -4661,18 +5558,18 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C60">
         <f>((anual!I60-anual!D60)/7)/anual!D60</f>
-        <v>9.7360515586771019E-3</v>
+        <v>6.8107718797761913E-3</v>
       </c>
       <c r="D60">
         <f>anual!C60</f>
-        <v>46040.071352808089</v>
+        <v>24209.971915413378</v>
       </c>
       <c r="E60" s="4">
         <f t="shared" si="0"/>
@@ -4681,18 +5578,18 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C61">
         <f>((anual!I61-anual!D61)/7)/anual!D61</f>
-        <v>4.2145146332176024E-3</v>
+        <v>9.7360515586771019E-3</v>
       </c>
       <c r="D61">
         <f>anual!C61</f>
-        <v>31572.870195090771</v>
+        <v>46040.071352808089</v>
       </c>
       <c r="E61" s="4">
         <f t="shared" si="0"/>
@@ -4701,18 +5598,18 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C62">
         <f>((anual!I62-anual!D62)/7)/anual!D62</f>
-        <v>1.203435200739461E-3</v>
+        <v>4.2145146332176024E-3</v>
       </c>
       <c r="D62">
         <f>anual!C62</f>
-        <v>19885.432570915815</v>
+        <v>31572.870195090771</v>
       </c>
       <c r="E62" s="4">
         <f t="shared" si="0"/>
@@ -4721,18 +5618,18 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C63">
         <f>((anual!I63-anual!D63)/7)/anual!D63</f>
-        <v>1.4196822064844467E-3</v>
+        <v>1.203435200739461E-3</v>
       </c>
       <c r="D63">
         <f>anual!C63</f>
-        <v>24550.259070555054</v>
+        <v>19885.432570915815</v>
       </c>
       <c r="E63" s="4">
         <f t="shared" si="0"/>
@@ -4741,18 +5638,18 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C64">
         <f>((anual!I64-anual!D64)/7)/anual!D64</f>
-        <v>-3.4891643205361582E-4</v>
+        <v>1.4196822064844467E-3</v>
       </c>
       <c r="D64">
         <f>anual!C64</f>
-        <v>11475.207717340756</v>
+        <v>24550.259070555054</v>
       </c>
       <c r="E64" s="4">
         <f t="shared" si="0"/>
@@ -4761,18 +5658,18 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C65">
         <f>((anual!I65-anual!D65)/7)/anual!D65</f>
-        <v>8.8018004980593024E-3</v>
+        <v>-3.4891643205361582E-4</v>
       </c>
       <c r="D65">
         <f>anual!C65</f>
-        <v>26061.852712436965</v>
+        <v>11475.207717340756</v>
       </c>
       <c r="E65" s="4">
         <f t="shared" si="0"/>
@@ -4781,18 +5678,18 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C66">
         <f>((anual!I66-anual!D66)/7)/anual!D66</f>
-        <v>1.3066881873625188E-3</v>
+        <v>8.8018004980593024E-3</v>
       </c>
       <c r="D66">
         <f>anual!C66</f>
-        <v>7102.1703459052405</v>
+        <v>26061.852712436965</v>
       </c>
       <c r="E66" s="4">
         <f t="shared" si="0"/>
@@ -4801,18 +5698,18 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>601</v>
+        <v>511</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C67">
         <f>((anual!I67-anual!D67)/7)/anual!D67</f>
-        <v>5.9649057179595906E-3</v>
+        <v>1.3066881873625188E-3</v>
       </c>
       <c r="D67">
         <f>anual!C67</f>
-        <v>137471.87134663673</v>
+        <v>7102.1703459052405</v>
       </c>
       <c r="E67" s="4">
         <f t="shared" si="0"/>
@@ -4821,58 +5718,58 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C68">
         <f>((anual!I68-anual!D68)/7)/anual!D68</f>
-        <v>7.3618030703158531E-3</v>
+        <v>5.9649057179595906E-3</v>
       </c>
       <c r="D68">
         <f>anual!C68</f>
-        <v>33409.314792378209</v>
+        <v>137471.87134663673</v>
       </c>
       <c r="E68" s="4">
-        <f t="shared" ref="E68:E86" si="1">5/53</f>
+        <f t="shared" si="0"/>
         <v>9.4339622641509441E-2</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C69">
         <f>((anual!I69-anual!D69)/7)/anual!D69</f>
-        <v>5.6121829058213852E-3</v>
+        <v>7.3618030703158531E-3</v>
       </c>
       <c r="D69">
         <f>anual!C69</f>
-        <v>52550.463292340683</v>
+        <v>33409.314792378209</v>
       </c>
       <c r="E69" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E69:E86" si="1">5/53</f>
         <v>9.4339622641509441E-2</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C70">
         <f>((anual!I70-anual!D70)/7)/anual!D70</f>
-        <v>3.2025609781807162E-3</v>
+        <v>5.6121829058213852E-3</v>
       </c>
       <c r="D70">
         <f>anual!C70</f>
-        <v>14564.88873797431</v>
+        <v>52550.463292340683</v>
       </c>
       <c r="E70" s="4">
         <f t="shared" si="1"/>
@@ -4881,18 +5778,18 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C71">
         <f>((anual!I71-anual!D71)/7)/anual!D71</f>
-        <v>-4.9502219245360244E-4</v>
+        <v>3.2025609781807162E-3</v>
       </c>
       <c r="D71">
         <f>anual!C71</f>
-        <v>29567.044098543542</v>
+        <v>14564.88873797431</v>
       </c>
       <c r="E71" s="4">
         <f t="shared" si="1"/>
@@ -4901,18 +5798,18 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C72">
         <f>((anual!I72-anual!D72)/7)/anual!D72</f>
-        <v>6.9381136846736581E-3</v>
+        <v>-4.9502219245360244E-4</v>
       </c>
       <c r="D72">
         <f>anual!C72</f>
-        <v>33050.969850982001</v>
+        <v>29567.044098543542</v>
       </c>
       <c r="E72" s="4">
         <f t="shared" si="1"/>
@@ -4921,18 +5818,18 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C73">
         <f>((anual!I73-anual!D73)/7)/anual!D73</f>
-        <v>-2.9708028972162562E-4</v>
+        <v>6.9381136846736581E-3</v>
       </c>
       <c r="D73">
         <f>anual!C73</f>
-        <v>32039.288694175266</v>
+        <v>33050.969850982001</v>
       </c>
       <c r="E73" s="4">
         <f t="shared" si="1"/>
@@ -4941,18 +5838,18 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C74">
         <f>((anual!I74-anual!D74)/7)/anual!D74</f>
-        <v>-2.9679669016130176E-3</v>
+        <v>-2.9708028972162562E-4</v>
       </c>
       <c r="D74">
         <f>anual!C74</f>
-        <v>36461.088623227894</v>
+        <v>32039.288694175266</v>
       </c>
       <c r="E74" s="4">
         <f t="shared" si="1"/>
@@ -4961,18 +5858,18 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C75">
         <f>((anual!I75-anual!D75)/7)/anual!D75</f>
-        <v>9.579872634006479E-3</v>
+        <v>-2.9679669016130176E-3</v>
       </c>
       <c r="D75">
         <f>anual!C75</f>
-        <v>20834.340359595444</v>
+        <v>36461.088623227894</v>
       </c>
       <c r="E75" s="4">
         <f t="shared" si="1"/>
@@ -4981,18 +5878,18 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C76">
         <f>((anual!I76-anual!D76)/7)/anual!D76</f>
-        <v>3.1887544107189175E-3</v>
+        <v>9.579872634006479E-3</v>
       </c>
       <c r="D76">
         <f>anual!C76</f>
-        <v>51926.454889730572</v>
+        <v>20834.340359595444</v>
       </c>
       <c r="E76" s="4">
         <f t="shared" si="1"/>
@@ -5001,18 +5898,18 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C77">
         <f>((anual!I77-anual!D77)/7)/anual!D77</f>
-        <v>1.5777518215040986E-2</v>
+        <v>3.1887544107189175E-3</v>
       </c>
       <c r="D77">
         <f>anual!C77</f>
-        <v>25410.003899916341</v>
+        <v>51926.454889730572</v>
       </c>
       <c r="E77" s="4">
         <f t="shared" si="1"/>
@@ -5021,18 +5918,18 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C78">
         <f>((anual!I78-anual!D78)/7)/anual!D78</f>
-        <v>2.8334736141647069E-3</v>
+        <v>1.5777518215040986E-2</v>
       </c>
       <c r="D78">
         <f>anual!C78</f>
-        <v>4723.7495104457066</v>
+        <v>25410.003899916341</v>
       </c>
       <c r="E78" s="4">
         <f t="shared" si="1"/>
@@ -5041,18 +5938,18 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C79">
         <f>((anual!I79-anual!D79)/7)/anual!D79</f>
-        <v>1.3670338421210378E-2</v>
+        <v>2.8334736141647069E-3</v>
       </c>
       <c r="D79">
         <f>anual!C79</f>
-        <v>12532.241626081443</v>
+        <v>4723.7495104457066</v>
       </c>
       <c r="E79" s="4">
         <f t="shared" si="1"/>
@@ -5061,18 +5958,18 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>701</v>
+        <v>613</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C80">
         <f>((anual!I80-anual!D80)/7)/anual!D80</f>
-        <v>-1.8325655232655121E-3</v>
+        <v>1.3670338421210378E-2</v>
       </c>
       <c r="D80">
         <f>anual!C80</f>
-        <v>93441.203508879888</v>
+        <v>12532.241626081443</v>
       </c>
       <c r="E80" s="4">
         <f t="shared" si="1"/>
@@ -5081,18 +5978,18 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C81">
         <f>((anual!I81-anual!D81)/7)/anual!D81</f>
-        <v>5.6549233603908162E-3</v>
+        <v>-1.8325655232655121E-3</v>
       </c>
       <c r="D81">
         <f>anual!C81</f>
-        <v>148901.97962131642</v>
+        <v>93441.203508879888</v>
       </c>
       <c r="E81" s="4">
         <f t="shared" si="1"/>
@@ -5101,18 +5998,18 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C82">
         <f>((anual!I82-anual!D82)/7)/anual!D82</f>
-        <v>5.3800249334947682E-4</v>
+        <v>5.6549233603908162E-3</v>
       </c>
       <c r="D82">
         <f>anual!C82</f>
-        <v>56935.574463207653</v>
+        <v>148901.97962131642</v>
       </c>
       <c r="E82" s="4">
         <f t="shared" si="1"/>
@@ -5121,18 +6018,18 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83">
         <f>((anual!I83-anual!D83)/7)/anual!D83</f>
-        <v>8.837789248615344E-3</v>
+        <v>5.3800249334947682E-4</v>
       </c>
       <c r="D83">
         <f>anual!C83</f>
-        <v>42872.750282955603</v>
+        <v>56935.574463207653</v>
       </c>
       <c r="E83" s="4">
         <f t="shared" si="1"/>
@@ -5141,18 +6038,18 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C84">
         <f>((anual!I84-anual!D84)/7)/anual!D84</f>
-        <v>3.5209375646829922E-3</v>
+        <v>8.837789248615344E-3</v>
       </c>
       <c r="D84">
         <f>anual!C84</f>
-        <v>44129.391173650161</v>
+        <v>42872.750282955603</v>
       </c>
       <c r="E84" s="4">
         <f t="shared" si="1"/>
@@ -5160,19 +6057,19 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="3">
-        <v>706</v>
+      <c r="A85" s="2">
+        <v>705</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C85">
         <f>((anual!I85-anual!D85)/7)/anual!D85</f>
-        <v>7.7234079986302972E-3</v>
+        <v>3.5209375646829922E-3</v>
       </c>
       <c r="D85">
         <f>anual!C85</f>
-        <v>55137.943035120479</v>
+        <v>44129.391173650161</v>
       </c>
       <c r="E85" s="4">
         <f t="shared" si="1"/>
@@ -5180,19 +6077,19 @@
       </c>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="5">
-        <v>0</v>
+      <c r="A86" s="3">
+        <v>706</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C86">
         <f>((anual!I86-anual!D86)/7)/anual!D86</f>
-        <v>3.9718671018175106E-3</v>
+        <v>7.7234079986302972E-3</v>
       </c>
       <c r="D86">
         <f>anual!C86</f>
-        <v>5020970.0892126299</v>
+        <v>55137.943035120479</v>
       </c>
       <c r="E86" s="4">
         <f t="shared" si="1"/>

--- a/data/raw/pob_anual.xlsx
+++ b/data/raw/pob_anual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://6f33fa7f78ea46e2aaca-my.sharepoint.com/personal/marianne_pena_ucr_ac_cr/Documents/cuenta personal/ucr pers/practica profesional/practica dengue/dengue-model/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="11_F25DC773A252ABDACC104827C19B4C825ADE58E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27D87B45-17B4-4D3A-8778-191323061B20}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="11_F25DC773A252ABDACC104827C19B4C825ADE58E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C38D23EF-D8AC-497D-8BA4-56B9BE161B09}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="94">
   <si>
     <t>https://admin.inec.cr/sites/default/files/2025-10/repoblaceppsubnaciopanelregionesmideplan2000-2050.xlsx</t>
   </si>
@@ -376,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -387,7 +387,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4373,13 +4372,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{517D5678-D518-4914-9735-1274804074C4}">
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>87</v>
       </c>
@@ -4392,11 +4391,8 @@
       <c r="D1" t="s">
         <v>89</v>
       </c>
-      <c r="E1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4404,19 +4400,15 @@
         <v>93</v>
       </c>
       <c r="C2">
-        <f>((anual!I2-anual!D2)/7)/anual!D2</f>
-        <v>3.9718671018175106E-3</v>
+        <f>(anual!J2-anual!C2)/(7*53-1)</f>
+        <v>530.60780876774493</v>
       </c>
       <c r="D2">
         <f>anual!C2</f>
         <v>5020970.0892126299</v>
       </c>
-      <c r="E2" s="4">
-        <f>5/53</f>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2">
         <v>101</v>
       </c>
@@ -4424,19 +4416,15 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <f>((anual!I3-anual!D3)/7)/anual!D3</f>
-        <v>1.868100218500498E-3</v>
+        <f>(anual!J3-anual!C3)/(7*53-1)</f>
+        <v>17.117450735373012</v>
       </c>
       <c r="D3">
         <f>anual!C3</f>
         <v>347692.45856501424</v>
       </c>
-      <c r="E3" s="4">
-        <f>5/53</f>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2">
         <v>102</v>
       </c>
@@ -4444,19 +4432,15 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <f>((anual!I4-anual!D4)/7)/anual!D4</f>
-        <v>3.1527798760231261E-3</v>
+        <f>(anual!J4-anual!C4)/(7*53-1)</f>
+        <v>5.7621343318431171</v>
       </c>
       <c r="D4">
         <f>anual!C4</f>
         <v>69342.771863127593</v>
       </c>
-      <c r="E4" s="4">
-        <f>5/53</f>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="2">
         <v>103</v>
       </c>
@@ -4464,19 +4448,15 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <f>((anual!I5-anual!D5)/7)/anual!D5</f>
-        <v>3.087060729904154E-3</v>
+        <f>(anual!J5-anual!C5)/(7*53-1)</f>
+        <v>19.550886718726424</v>
       </c>
       <c r="D5">
         <f>anual!C5</f>
         <v>238762.28232309327</v>
       </c>
-      <c r="E5" s="4">
-        <f t="shared" ref="E5:E68" si="0">5/53</f>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="2">
         <v>104</v>
       </c>
@@ -4484,19 +4464,15 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <f>((anual!I6-anual!D6)/7)/anual!D6</f>
-        <v>2.9674075772079603E-3</v>
+        <f>(anual!J6-anual!C6)/(7*53-1)</f>
+        <v>3.0158987592872331</v>
       </c>
       <c r="D6">
         <f>anual!C6</f>
         <v>38240.587050800503</v>
       </c>
-      <c r="E6" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="2">
         <v>105</v>
       </c>
@@ -4504,19 +4480,15 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <f>((anual!I7-anual!D7)/7)/anual!D7</f>
-        <v>1.0804017806949633E-3</v>
+        <f>(anual!J7-anual!C7)/(7*53-1)</f>
+        <v>0.51279102889257533</v>
       </c>
       <c r="D7">
         <f>anual!C7</f>
         <v>17842.632764587546</v>
       </c>
-      <c r="E7" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="2">
         <v>106</v>
       </c>
@@ -4524,19 +4496,15 @@
         <v>8</v>
       </c>
       <c r="C8">
-        <f>((anual!I8-anual!D8)/7)/anual!D8</f>
-        <v>2.2427367342404908E-3</v>
+        <f>(anual!J8-anual!C8)/(7*53-1)</f>
+        <v>3.6762378521639985</v>
       </c>
       <c r="D8">
         <f>anual!C8</f>
         <v>61640.79175785082</v>
       </c>
-      <c r="E8" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="2">
         <v>107</v>
       </c>
@@ -4544,19 +4512,15 @@
         <v>9</v>
       </c>
       <c r="C9">
-        <f>((anual!I9-anual!D9)/7)/anual!D9</f>
-        <v>2.0638506204688394E-3</v>
+        <f>(anual!J9-anual!C9)/(7*53-1)</f>
+        <v>1.5226121034181159</v>
       </c>
       <c r="D9">
         <f>anual!C9</f>
         <v>28301.543605497558</v>
       </c>
-      <c r="E9" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="2">
         <v>108</v>
       </c>
@@ -4564,19 +4528,15 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <f>((anual!I10-anual!D10)/7)/anual!D10</f>
-        <v>2.5998944003007085E-3</v>
+        <f>(anual!J10-anual!C10)/(7*53-1)</f>
+        <v>9.4353102105397522</v>
       </c>
       <c r="D10">
         <f>anual!C10</f>
         <v>137108.97722321076</v>
       </c>
-      <c r="E10" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="2">
         <v>109</v>
       </c>
@@ -4584,19 +4544,15 @@
         <v>11</v>
       </c>
       <c r="C11">
-        <f>((anual!I11-anual!D11)/7)/anual!D11</f>
-        <v>5.5331855705229279E-3</v>
+        <f>(anual!J11-anual!C11)/(7*53-1)</f>
+        <v>8.717326802152467</v>
       </c>
       <c r="D11">
         <f>anual!C11</f>
         <v>59327.717623552853</v>
       </c>
-      <c r="E11" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="2">
         <v>110</v>
       </c>
@@ -4604,19 +4560,15 @@
         <v>12</v>
       </c>
       <c r="C12">
-        <f>((anual!I12-anual!D12)/7)/anual!D12</f>
-        <v>6.0189412595965733E-3</v>
+        <f>(anual!J12-anual!C12)/(7*53-1)</f>
+        <v>14.932331722383498</v>
       </c>
       <c r="D12">
         <f>anual!C12</f>
         <v>92686.07744882835</v>
       </c>
-      <c r="E12" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="2">
         <v>111</v>
       </c>
@@ -4624,19 +4576,15 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <f>((anual!I13-anual!D13)/7)/anual!D13</f>
-        <v>3.7542523553232084E-3</v>
+        <f>(anual!J13-anual!C13)/(7*53-1)</f>
+        <v>6.9464576116092882</v>
       </c>
       <c r="D13">
         <f>anual!C13</f>
         <v>69754.925417826904</v>
       </c>
-      <c r="E13" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2">
         <v>112</v>
       </c>
@@ -4644,19 +4592,15 @@
         <v>14</v>
       </c>
       <c r="C14">
-        <f>((anual!I14-anual!D14)/7)/anual!D14</f>
-        <v>1.5256857218822817E-3</v>
+        <f>(anual!J14-anual!C14)/(7*53-1)</f>
+        <v>0.90387226073778304</v>
       </c>
       <c r="D14">
         <f>anual!C14</f>
         <v>21699.266475138473</v>
       </c>
-      <c r="E14" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2">
         <v>113</v>
       </c>
@@ -4664,19 +4608,15 @@
         <v>15</v>
       </c>
       <c r="C15">
-        <f>((anual!I15-anual!D15)/7)/anual!D15</f>
-        <v>2.3705404429928863E-3</v>
+        <f>(anual!J15-anual!C15)/(7*53-1)</f>
+        <v>5.2439428247564877</v>
       </c>
       <c r="D15">
         <f>anual!C15</f>
         <v>83692.119332512375</v>
       </c>
-      <c r="E15" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2">
         <v>114</v>
       </c>
@@ -4684,19 +4624,15 @@
         <v>16</v>
       </c>
       <c r="C16">
-        <f>((anual!I16-anual!D16)/7)/anual!D16</f>
-        <v>9.4827452934470851E-4</v>
+        <f>(anual!J16-anual!C16)/(7*53-1)</f>
+        <v>1.5141194548890091</v>
       </c>
       <c r="D16">
         <f>anual!C16</f>
         <v>61121.852323967265</v>
       </c>
-      <c r="E16" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="2">
         <v>115</v>
       </c>
@@ -4704,19 +4640,15 @@
         <v>17</v>
       </c>
       <c r="C17">
-        <f>((anual!I17-anual!D17)/7)/anual!D17</f>
-        <v>-5.3284409479437069E-4</v>
+        <f>(anual!J17-anual!C17)/(7*53-1)</f>
+        <v>-0.87984472655447754</v>
       </c>
       <c r="D17">
         <f>anual!C17</f>
         <v>61401.434959428974</v>
       </c>
-      <c r="E17" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="2">
         <v>116</v>
       </c>
@@ -4724,19 +4656,15 @@
         <v>18</v>
       </c>
       <c r="C18">
-        <f>((anual!I18-anual!D18)/7)/anual!D18</f>
-        <v>4.5148043493114355E-3</v>
+        <f>(anual!J18-anual!C18)/(7*53-1)</f>
+        <v>0.86311678662558655</v>
       </c>
       <c r="D18">
         <f>anual!C18</f>
         <v>7122.4202578776185</v>
       </c>
-      <c r="E18" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="2">
         <v>117</v>
       </c>
@@ -4744,19 +4672,15 @@
         <v>19</v>
       </c>
       <c r="C19">
-        <f>((anual!I19-anual!D19)/7)/anual!D19</f>
-        <v>5.9882081108790237E-4</v>
+        <f>(anual!J19-anual!C19)/(7*53-1)</f>
+        <v>0.13055669687950333</v>
       </c>
       <c r="D19">
         <f>anual!C19</f>
         <v>7759.3518669735276</v>
       </c>
-      <c r="E19" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="2">
         <v>118</v>
       </c>
@@ -4764,19 +4688,15 @@
         <v>20</v>
       </c>
       <c r="C20">
-        <f>((anual!I20-anual!D20)/7)/anual!D20</f>
-        <v>2.0284040722509987E-3</v>
+        <f>(anual!J20-anual!C20)/(7*53-1)</f>
+        <v>4.2085491510450677</v>
       </c>
       <c r="D20">
         <f>anual!C20</f>
         <v>78069.636218031286</v>
       </c>
-      <c r="E20" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="2">
         <v>119</v>
       </c>
@@ -4784,19 +4704,15 @@
         <v>21</v>
       </c>
       <c r="C21">
-        <f>((anual!I21-anual!D21)/7)/anual!D21</f>
-        <v>-1.8406580355975945E-3</v>
+        <f>(anual!J21-anual!C21)/(7*53-1)</f>
+        <v>-6.6737217915584992</v>
       </c>
       <c r="D21">
         <f>anual!C21</f>
         <v>135629.67197663515</v>
       </c>
-      <c r="E21" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="2">
         <v>120</v>
       </c>
@@ -4804,19 +4720,15 @@
         <v>22</v>
       </c>
       <c r="C22">
-        <f>((anual!I22-anual!D22)/7)/anual!D22</f>
-        <v>3.4707894205274446E-3</v>
+        <f>(anual!J22-anual!C22)/(7*53-1)</f>
+        <v>1.207598887725023</v>
       </c>
       <c r="D22">
         <f>anual!C22</f>
         <v>13110.005500423718</v>
       </c>
-      <c r="E22" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" s="2">
         <v>201</v>
       </c>
@@ -4824,19 +4736,15 @@
         <v>23</v>
       </c>
       <c r="C23">
-        <f>((anual!I23-anual!D23)/7)/anual!D23</f>
-        <v>5.4598986657930669E-3</v>
+        <f>(anual!J23-anual!C23)/(7*53-1)</f>
+        <v>45.52500488298341</v>
       </c>
       <c r="D23">
         <f>anual!C23</f>
         <v>313360.92561695981</v>
       </c>
-      <c r="E23" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="2">
         <v>202</v>
       </c>
@@ -4844,19 +4752,15 @@
         <v>24</v>
       </c>
       <c r="C24">
-        <f>((anual!I24-anual!D24)/7)/anual!D24</f>
-        <v>4.3743395004128211E-3</v>
+        <f>(anual!J24-anual!C24)/(7*53-1)</f>
+        <v>10.275650653118351</v>
       </c>
       <c r="D24">
         <f>anual!C24</f>
         <v>89238.4691379383</v>
       </c>
-      <c r="E24" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="2">
         <v>203</v>
       </c>
@@ -4864,19 +4768,15 @@
         <v>25</v>
       </c>
       <c r="C25">
-        <f>((anual!I25-anual!D25)/7)/anual!D25</f>
-        <v>4.5811336827644303E-3</v>
+        <f>(anual!J25-anual!C25)/(7*53-1)</f>
+        <v>9.4895560536177275</v>
       </c>
       <c r="D25">
         <f>anual!C25</f>
         <v>77877.077161967609</v>
       </c>
-      <c r="E25" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="2">
         <v>204</v>
       </c>
@@ -4884,19 +4784,15 @@
         <v>26</v>
       </c>
       <c r="C26">
-        <f>((anual!I26-anual!D26)/7)/anual!D26</f>
-        <v>3.5509672576142549E-3</v>
+        <f>(anual!J26-anual!C26)/(7*53-1)</f>
+        <v>0.69892638897284798</v>
       </c>
       <c r="D26">
         <f>anual!C26</f>
         <v>7320.929017146681</v>
       </c>
-      <c r="E26" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="2">
         <v>205</v>
       </c>
@@ -4904,19 +4800,15 @@
         <v>27</v>
       </c>
       <c r="C27">
-        <f>((anual!I27-anual!D27)/7)/anual!D27</f>
-        <v>3.9986888451666348E-3</v>
+        <f>(anual!J27-anual!C27)/(7*53-1)</f>
+        <v>3.1346061050766219</v>
       </c>
       <c r="D27">
         <f>anual!C27</f>
         <v>29541.082982532505</v>
       </c>
-      <c r="E27" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="2">
         <v>206</v>
       </c>
@@ -4924,19 +4816,15 @@
         <v>28</v>
       </c>
       <c r="C28">
-        <f>((anual!I28-anual!D28)/7)/anual!D28</f>
-        <v>3.812647734999011E-3</v>
+        <f>(anual!J28-anual!C28)/(7*53-1)</f>
+        <v>4.9483622357434109</v>
       </c>
       <c r="D28">
         <f>anual!C28</f>
         <v>48765.107980937304</v>
       </c>
-      <c r="E28" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" s="2">
         <v>207</v>
       </c>
@@ -4944,19 +4832,15 @@
         <v>29</v>
       </c>
       <c r="C29">
-        <f>((anual!I29-anual!D29)/7)/anual!D29</f>
-        <v>5.0224082644080353E-3</v>
+        <f>(anual!J29-anual!C29)/(7*53-1)</f>
+        <v>5.4667185972246095</v>
       </c>
       <c r="D29">
         <f>anual!C29</f>
         <v>40963.256483213729</v>
       </c>
-      <c r="E29" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" s="2">
         <v>208</v>
       </c>
@@ -4964,19 +4848,15 @@
         <v>30</v>
       </c>
       <c r="C30">
-        <f>((anual!I30-anual!D30)/7)/anual!D30</f>
-        <v>5.9951805849104709E-3</v>
+        <f>(anual!J30-anual!C30)/(7*53-1)</f>
+        <v>5.4186630055280025</v>
       </c>
       <c r="D30">
         <f>anual!C30</f>
         <v>33882.600982043499</v>
       </c>
-      <c r="E30" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="2">
         <v>209</v>
       </c>
@@ -4984,19 +4864,15 @@
         <v>31</v>
       </c>
       <c r="C31">
-        <f>((anual!I31-anual!D31)/7)/anual!D31</f>
-        <v>6.5649523334877563E-3</v>
+        <f>(anual!J31-anual!C31)/(7*53-1)</f>
+        <v>4.1857436145061637</v>
       </c>
       <c r="D31">
         <f>anual!C31</f>
         <v>23883.945695728271</v>
       </c>
-      <c r="E31" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="2">
         <v>210</v>
       </c>
@@ -5004,19 +4880,15 @@
         <v>32</v>
       </c>
       <c r="C32">
-        <f>((anual!I32-anual!D32)/7)/anual!D32</f>
-        <v>6.5438608113860194E-3</v>
+        <f>(anual!J32-anual!C32)/(7*53-1)</f>
+        <v>35.177617759214137</v>
       </c>
       <c r="D32">
         <f>anual!C32</f>
         <v>200446.33903553456</v>
       </c>
-      <c r="E32" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="2">
         <v>211</v>
       </c>
@@ -5024,19 +4896,15 @@
         <v>33</v>
       </c>
       <c r="C33">
-        <f>((anual!I33-anual!D33)/7)/anual!D33</f>
-        <v>3.4531094457913684E-3</v>
+        <f>(anual!J33-anual!C33)/(7*53-1)</f>
+        <v>1.3384261768174346</v>
       </c>
       <c r="D33">
         <f>anual!C33</f>
         <v>14410.500892204112</v>
       </c>
-      <c r="E33" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="2">
         <v>212</v>
       </c>
@@ -5044,19 +4912,15 @@
         <v>34</v>
       </c>
       <c r="C34">
-        <f>((anual!I34-anual!D34)/7)/anual!D34</f>
-        <v>3.5841874694335094E-3</v>
+        <f>(anual!J34-anual!C34)/(7*53-1)</f>
+        <v>2.1195688388373299</v>
       </c>
       <c r="D34">
         <f>anual!C34</f>
         <v>22165.483844052134</v>
       </c>
-      <c r="E34" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="2">
         <v>213</v>
       </c>
@@ -5064,19 +4928,15 @@
         <v>35</v>
       </c>
       <c r="C35">
-        <f>((anual!I35-anual!D35)/7)/anual!D35</f>
-        <v>5.3724116208518939E-3</v>
+        <f>(anual!J35-anual!C35)/(7*53-1)</f>
+        <v>7.8366778650628426</v>
       </c>
       <c r="D35">
         <f>anual!C35</f>
         <v>54442.633617922635</v>
       </c>
-      <c r="E35" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" s="2">
         <v>214</v>
       </c>
@@ -5084,19 +4944,15 @@
         <v>36</v>
       </c>
       <c r="C36">
-        <f>((anual!I36-anual!D36)/7)/anual!D36</f>
-        <v>1.1409413530946664E-2</v>
+        <f>(anual!J36-anual!C36)/(7*53-1)</f>
+        <v>10.475144849125767</v>
       </c>
       <c r="D36">
         <f>anual!C36</f>
         <v>34045.178955669733</v>
       </c>
-      <c r="E36" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" s="2">
         <v>215</v>
       </c>
@@ -5104,19 +4960,15 @@
         <v>37</v>
       </c>
       <c r="C37">
-        <f>((anual!I37-anual!D37)/7)/anual!D37</f>
-        <v>4.9476740207180722E-3</v>
+        <f>(anual!J37-anual!C37)/(7*53-1)</f>
+        <v>2.5363970395470017</v>
       </c>
       <c r="D37">
         <f>anual!C37</f>
         <v>19166.649236339777</v>
       </c>
-      <c r="E37" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" s="2">
         <v>216</v>
       </c>
@@ -5124,19 +4976,15 @@
         <v>38</v>
       </c>
       <c r="C38">
-        <f>((anual!I38-anual!D38)/7)/anual!D38</f>
-        <v>1.0201788943689527E-2</v>
+        <f>(anual!J38-anual!C38)/(7*53-1)</f>
+        <v>4.5709855506309198</v>
       </c>
       <c r="D38">
         <f>anual!C38</f>
         <v>16589.593831471066</v>
       </c>
-      <c r="E38" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" s="2">
         <v>301</v>
       </c>
@@ -5144,19 +4992,15 @@
         <v>39</v>
       </c>
       <c r="C39">
-        <f>((anual!I39-anual!D39)/7)/anual!D39</f>
-        <v>1.7631233970079299E-3</v>
+        <f>(anual!J39-anual!C39)/(7*53-1)</f>
+        <v>7.4906878928820655</v>
       </c>
       <c r="D39">
         <f>anual!C39</f>
         <v>160800.54777507891</v>
       </c>
-      <c r="E39" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="2">
         <v>302</v>
       </c>
@@ -5164,19 +5008,15 @@
         <v>40</v>
       </c>
       <c r="C40">
-        <f>((anual!I40-anual!D40)/7)/anual!D40</f>
-        <v>1.9409233851842747E-3</v>
+        <f>(anual!J40-anual!C40)/(7*53-1)</f>
+        <v>3.1090818132319082</v>
       </c>
       <c r="D40">
         <f>anual!C40</f>
         <v>60503.614472114554</v>
       </c>
-      <c r="E40" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="2">
         <v>303</v>
       </c>
@@ -5184,19 +5024,15 @@
         <v>41</v>
       </c>
       <c r="C41">
-        <f>((anual!I41-anual!D41)/7)/anual!D41</f>
-        <v>3.2813645124535793E-3</v>
+        <f>(anual!J41-anual!C41)/(7*53-1)</f>
+        <v>9.6780498205634959</v>
       </c>
       <c r="D41">
         <f>anual!C41</f>
         <v>111181.99268416413</v>
       </c>
-      <c r="E41" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="2">
         <v>304</v>
       </c>
@@ -5204,19 +5040,15 @@
         <v>42</v>
       </c>
       <c r="C42">
-        <f>((anual!I42-anual!D42)/7)/anual!D42</f>
-        <v>-1.875319691834949E-3</v>
+        <f>(anual!J42-anual!C42)/(7*53-1)</f>
+        <v>-0.7921609935600753</v>
       </c>
       <c r="D42">
         <f>anual!C42</f>
         <v>16013.572967355041</v>
       </c>
-      <c r="E42" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" s="2">
         <v>305</v>
       </c>
@@ -5224,19 +5056,15 @@
         <v>43</v>
       </c>
       <c r="C43">
-        <f>((anual!I43-anual!D43)/7)/anual!D43</f>
-        <v>-2.8414147425063594E-3</v>
+        <f>(anual!J43-anual!C43)/(7*53-1)</f>
+        <v>-5.2962071473187944</v>
       </c>
       <c r="D43">
         <f>anual!C43</f>
         <v>70325.525267318735</v>
       </c>
-      <c r="E43" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" s="2">
         <v>306</v>
       </c>
@@ -5244,19 +5072,15 @@
         <v>44</v>
       </c>
       <c r="C44">
-        <f>((anual!I44-anual!D44)/7)/anual!D44</f>
-        <v>1.027499633523098E-3</v>
+        <f>(anual!J44-anual!C44)/(7*53-1)</f>
+        <v>0.40951121319967815</v>
       </c>
       <c r="D44">
         <f>anual!C44</f>
         <v>15059.088779095084</v>
       </c>
-      <c r="E44" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" s="2">
         <v>307</v>
       </c>
@@ -5264,19 +5088,15 @@
         <v>45</v>
       </c>
       <c r="C45">
-        <f>((anual!I45-anual!D45)/7)/anual!D45</f>
-        <v>1.586539610801402E-3</v>
+        <f>(anual!J45-anual!C45)/(7*53-1)</f>
+        <v>2.014162363693794</v>
       </c>
       <c r="D45">
         <f>anual!C45</f>
         <v>48159.580867468983</v>
       </c>
-      <c r="E45" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" s="2">
         <v>308</v>
       </c>
@@ -5284,19 +5104,15 @@
         <v>46</v>
       </c>
       <c r="C46">
-        <f>((anual!I46-anual!D46)/7)/anual!D46</f>
-        <v>1.9796925213435004E-3</v>
+        <f>(anual!J46-anual!C46)/(7*53-1)</f>
+        <v>2.3320366876068874</v>
       </c>
       <c r="D46">
         <f>anual!C46</f>
         <v>44512.114468701118</v>
       </c>
-      <c r="E46" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" s="2">
         <v>401</v>
       </c>
@@ -5304,19 +5120,15 @@
         <v>47</v>
       </c>
       <c r="C47">
-        <f>((anual!I47-anual!D47)/7)/anual!D47</f>
-        <v>4.417625643832134E-3</v>
+        <f>(anual!J47-anual!C47)/(7*53-1)</f>
+        <v>16.529338970875077</v>
       </c>
       <c r="D47">
         <f>anual!C47</f>
         <v>141279.33236905705</v>
       </c>
-      <c r="E47" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" s="2">
         <v>402</v>
       </c>
@@ -5324,19 +5136,15 @@
         <v>48</v>
       </c>
       <c r="C48">
-        <f>((anual!I48-anual!D48)/7)/anual!D48</f>
-        <v>6.1172090172660109E-3</v>
+        <f>(anual!J48-anual!C48)/(7*53-1)</f>
+        <v>7.576650353867759</v>
       </c>
       <c r="D48">
         <f>anual!C48</f>
         <v>46412.577574639348</v>
       </c>
-      <c r="E48" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" s="2">
         <v>403</v>
       </c>
@@ -5344,19 +5152,15 @@
         <v>49</v>
       </c>
       <c r="C49">
-        <f>((anual!I49-anual!D49)/7)/anual!D49</f>
-        <v>3.3805719623731241E-3</v>
+        <f>(anual!J49-anual!C49)/(7*53-1)</f>
+        <v>4.3339698715152561</v>
       </c>
       <c r="D49">
         <f>anual!C49</f>
         <v>48618.467107528188</v>
       </c>
-      <c r="E49" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" s="2">
         <v>404</v>
       </c>
@@ -5364,19 +5168,15 @@
         <v>50</v>
       </c>
       <c r="C50">
-        <f>((anual!I50-anual!D50)/7)/anual!D50</f>
-        <v>5.7772007659230677E-3</v>
+        <f>(anual!J50-anual!C50)/(7*53-1)</f>
+        <v>6.701859499201138</v>
       </c>
       <c r="D50">
         <f>anual!C50</f>
         <v>42982.873210465354</v>
       </c>
-      <c r="E50" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" s="2">
         <v>405</v>
       </c>
@@ -5384,19 +5184,15 @@
         <v>51</v>
       </c>
       <c r="C51">
-        <f>((anual!I51-anual!D51)/7)/anual!D51</f>
-        <v>5.2870262626682684E-3</v>
+        <f>(anual!J51-anual!C51)/(7*53-1)</f>
+        <v>7.6224060020618758</v>
       </c>
       <c r="D51">
         <f>anual!C51</f>
         <v>54313.580033103179</v>
       </c>
-      <c r="E51" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" s="2">
         <v>406</v>
       </c>
@@ -5404,19 +5200,15 @@
         <v>52</v>
       </c>
       <c r="C52">
-        <f>((anual!I52-anual!D52)/7)/anual!D52</f>
-        <v>3.7952413768835049E-3</v>
+        <f>(anual!J52-anual!C52)/(7*53-1)</f>
+        <v>2.3031767929389635</v>
       </c>
       <c r="D52">
         <f>anual!C52</f>
         <v>22740.240755341045</v>
       </c>
-      <c r="E52" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" s="2">
         <v>407</v>
       </c>
@@ -5424,19 +5216,15 @@
         <v>53</v>
       </c>
       <c r="C53">
-        <f>((anual!I53-anual!D53)/7)/anual!D53</f>
-        <v>3.115418895730318E-3</v>
+        <f>(anual!J53-anual!C53)/(7*53-1)</f>
+        <v>2.1667629107253781</v>
       </c>
       <c r="D53">
         <f>anual!C53</f>
         <v>25802.988492663877</v>
       </c>
-      <c r="E53" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" s="2">
         <v>408</v>
       </c>
@@ -5444,19 +5232,15 @@
         <v>54</v>
       </c>
       <c r="C54">
-        <f>((anual!I54-anual!D54)/7)/anual!D54</f>
-        <v>5.2621279143333392E-3</v>
+        <f>(anual!J54-anual!C54)/(7*53-1)</f>
+        <v>2.9645573135163925</v>
       </c>
       <c r="D54">
         <f>anual!C54</f>
         <v>21193.070036267593</v>
       </c>
-      <c r="E54" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" s="2">
         <v>409</v>
       </c>
@@ -5464,19 +5248,15 @@
         <v>55</v>
       </c>
       <c r="C55">
-        <f>((anual!I55-anual!D55)/7)/anual!D55</f>
-        <v>1.2046976212780362E-3</v>
+        <f>(anual!J55-anual!C55)/(7*53-1)</f>
+        <v>0.95052942804489959</v>
       </c>
       <c r="D55">
         <f>anual!C55</f>
         <v>30125.956695576082</v>
       </c>
-      <c r="E55" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" s="2">
         <v>410</v>
       </c>
@@ -5484,19 +5264,15 @@
         <v>56</v>
       </c>
       <c r="C56">
-        <f>((anual!I56-anual!D56)/7)/anual!D56</f>
-        <v>1.4048524325157918E-2</v>
+        <f>(anual!J56-anual!C56)/(7*53-1)</f>
+        <v>32.747487946080888</v>
       </c>
       <c r="D56">
         <f>anual!C56</f>
         <v>86102.105355116975</v>
       </c>
-      <c r="E56" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" s="2">
         <v>501</v>
       </c>
@@ -5504,19 +5280,15 @@
         <v>57</v>
       </c>
       <c r="C57">
-        <f>((anual!I57-anual!D57)/7)/anual!D57</f>
-        <v>8.5168759246700143E-3</v>
+        <f>(anual!J57-anual!C57)/(7*53-1)</f>
+        <v>17.408047296890771</v>
       </c>
       <c r="D57">
         <f>anual!C57</f>
         <v>76113.681382974697</v>
       </c>
-      <c r="E57" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58" s="2">
         <v>502</v>
       </c>
@@ -5524,19 +5296,15 @@
         <v>58</v>
       </c>
       <c r="C58">
-        <f>((anual!I58-anual!D58)/7)/anual!D58</f>
-        <v>3.6837367636312524E-3</v>
+        <f>(anual!J58-anual!C58)/(7*53-1)</f>
+        <v>5.618464288649065</v>
       </c>
       <c r="D58">
         <f>anual!C58</f>
         <v>57161.818517786087</v>
       </c>
-      <c r="E58" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" s="2">
         <v>503</v>
       </c>
@@ -5544,19 +5312,15 @@
         <v>59</v>
       </c>
       <c r="C59">
-        <f>((anual!I59-anual!D59)/7)/anual!D59</f>
-        <v>8.479829388756556E-3</v>
+        <f>(anual!J59-anual!C59)/(7*53-1)</f>
+        <v>15.557225386171037</v>
       </c>
       <c r="D59">
         <f>anual!C59</f>
         <v>68302.663687150722</v>
       </c>
-      <c r="E59" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" s="2">
         <v>504</v>
       </c>
@@ -5564,19 +5328,15 @@
         <v>60</v>
       </c>
       <c r="C60">
-        <f>((anual!I60-anual!D60)/7)/anual!D60</f>
-        <v>6.8107718797761913E-3</v>
+        <f>(anual!J60-anual!C60)/(7*53-1)</f>
+        <v>4.4165663970217057</v>
       </c>
       <c r="D60">
         <f>anual!C60</f>
         <v>24209.971915413378</v>
       </c>
-      <c r="E60" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" s="2">
         <v>505</v>
       </c>
@@ -5584,19 +5344,15 @@
         <v>61</v>
       </c>
       <c r="C61">
-        <f>((anual!I61-anual!D61)/7)/anual!D61</f>
-        <v>9.7360515586771019E-3</v>
+        <f>(anual!J61-anual!C61)/(7*53-1)</f>
+        <v>12.050637072217443</v>
       </c>
       <c r="D61">
         <f>anual!C61</f>
         <v>46040.071352808089</v>
       </c>
-      <c r="E61" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" s="2">
         <v>506</v>
       </c>
@@ -5604,19 +5360,15 @@
         <v>62</v>
       </c>
       <c r="C62">
-        <f>((anual!I62-anual!D62)/7)/anual!D62</f>
-        <v>4.2145146332176024E-3</v>
+        <f>(anual!J62-anual!C62)/(7*53-1)</f>
+        <v>3.5542941028352533</v>
       </c>
       <c r="D62">
         <f>anual!C62</f>
         <v>31572.870195090771</v>
       </c>
-      <c r="E62" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" s="2">
         <v>507</v>
       </c>
@@ -5624,19 +5376,15 @@
         <v>63</v>
       </c>
       <c r="C63">
-        <f>((anual!I63-anual!D63)/7)/anual!D63</f>
-        <v>1.203435200739461E-3</v>
+        <f>(anual!J63-anual!C63)/(7*53-1)</f>
+        <v>0.63982083263925582</v>
       </c>
       <c r="D63">
         <f>anual!C63</f>
         <v>19885.432570915815</v>
       </c>
-      <c r="E63" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" s="2">
         <v>508</v>
       </c>
@@ -5644,19 +5392,15 @@
         <v>64</v>
       </c>
       <c r="C64">
-        <f>((anual!I64-anual!D64)/7)/anual!D64</f>
-        <v>1.4196822064844467E-3</v>
+        <f>(anual!J64-anual!C64)/(7*53-1)</f>
+        <v>0.941811627175972</v>
       </c>
       <c r="D64">
         <f>anual!C64</f>
         <v>24550.259070555054</v>
       </c>
-      <c r="E64" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" s="2">
         <v>509</v>
       </c>
@@ -5664,19 +5408,15 @@
         <v>65</v>
       </c>
       <c r="C65">
-        <f>((anual!I65-anual!D65)/7)/anual!D65</f>
-        <v>-3.4891643205361582E-4</v>
+        <f>(anual!J65-anual!C65)/(7*53-1)</f>
+        <v>-7.7765536849442832E-2</v>
       </c>
       <c r="D65">
         <f>anual!C65</f>
         <v>11475.207717340756</v>
       </c>
-      <c r="E65" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" s="2">
         <v>510</v>
       </c>
@@ -5684,19 +5424,15 @@
         <v>66</v>
       </c>
       <c r="C66">
-        <f>((anual!I66-anual!D66)/7)/anual!D66</f>
-        <v>8.8018004980593024E-3</v>
+        <f>(anual!J66-anual!C66)/(7*53-1)</f>
+        <v>6.2113557300707454</v>
       </c>
       <c r="D66">
         <f>anual!C66</f>
         <v>26061.852712436965</v>
       </c>
-      <c r="E66" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" s="2">
         <v>511</v>
       </c>
@@ -5704,19 +5440,15 @@
         <v>67</v>
       </c>
       <c r="C67">
-        <f>((anual!I67-anual!D67)/7)/anual!D67</f>
-        <v>1.3066881873625188E-3</v>
+        <f>(anual!J67-anual!C67)/(7*53-1)</f>
+        <v>0.21987370697168052</v>
       </c>
       <c r="D67">
         <f>anual!C67</f>
         <v>7102.1703459052405</v>
       </c>
-      <c r="E67" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" s="2">
         <v>601</v>
       </c>
@@ -5724,19 +5456,15 @@
         <v>68</v>
       </c>
       <c r="C68">
-        <f>((anual!I68-anual!D68)/7)/anual!D68</f>
-        <v>5.9649057179595906E-3</v>
+        <f>(anual!J68-anual!C68)/(7*53-1)</f>
+        <v>21.903672674075523</v>
       </c>
       <c r="D68">
         <f>anual!C68</f>
         <v>137471.87134663673</v>
       </c>
-      <c r="E68" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" s="2">
         <v>602</v>
       </c>
@@ -5744,19 +5472,15 @@
         <v>69</v>
       </c>
       <c r="C69">
-        <f>((anual!I69-anual!D69)/7)/anual!D69</f>
-        <v>7.3618030703158531E-3</v>
+        <f>(anual!J69-anual!C69)/(7*53-1)</f>
+        <v>6.5307926435859294</v>
       </c>
       <c r="D69">
         <f>anual!C69</f>
         <v>33409.314792378209</v>
       </c>
-      <c r="E69" s="4">
-        <f t="shared" ref="E69:E86" si="1">5/53</f>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" s="2">
         <v>603</v>
       </c>
@@ -5764,19 +5488,15 @@
         <v>70</v>
       </c>
       <c r="C70">
-        <f>((anual!I70-anual!D70)/7)/anual!D70</f>
-        <v>5.6121829058213852E-3</v>
+        <f>(anual!J70-anual!C70)/(7*53-1)</f>
+        <v>7.8963392792623353</v>
       </c>
       <c r="D70">
         <f>anual!C70</f>
         <v>52550.463292340683</v>
       </c>
-      <c r="E70" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" s="2">
         <v>604</v>
       </c>
@@ -5784,19 +5504,15 @@
         <v>71</v>
       </c>
       <c r="C71">
-        <f>((anual!I71-anual!D71)/7)/anual!D71</f>
-        <v>3.2025609781807162E-3</v>
+        <f>(anual!J71-anual!C71)/(7*53-1)</f>
+        <v>1.253065004080093</v>
       </c>
       <c r="D71">
         <f>anual!C71</f>
         <v>14564.88873797431</v>
       </c>
-      <c r="E71" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" s="2">
         <v>605</v>
       </c>
@@ -5804,19 +5520,15 @@
         <v>72</v>
       </c>
       <c r="C72">
-        <f>((anual!I72-anual!D72)/7)/anual!D72</f>
-        <v>-4.9502219245360244E-4</v>
+        <f>(anual!J72-anual!C72)/(7*53-1)</f>
+        <v>-0.38191104546550941</v>
       </c>
       <c r="D72">
         <f>anual!C72</f>
         <v>29567.044098543542</v>
       </c>
-      <c r="E72" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" s="2">
         <v>606</v>
       </c>
@@ -5824,19 +5536,15 @@
         <v>73</v>
       </c>
       <c r="C73">
-        <f>((anual!I73-anual!D73)/7)/anual!D73</f>
-        <v>6.9381136846736581E-3</v>
+        <f>(anual!J73-anual!C73)/(7*53-1)</f>
+        <v>6.1421946863664667</v>
       </c>
       <c r="D73">
         <f>anual!C73</f>
         <v>33050.969850982001</v>
       </c>
-      <c r="E73" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" s="2">
         <v>607</v>
       </c>
@@ -5844,19 +5552,15 @@
         <v>74</v>
       </c>
       <c r="C74">
-        <f>((anual!I74-anual!D74)/7)/anual!D74</f>
-        <v>-2.9708028972162562E-4</v>
+        <f>(anual!J74-anual!C74)/(7*53-1)</f>
+        <v>-0.24418752315783374</v>
       </c>
       <c r="D74">
         <f>anual!C74</f>
         <v>32039.288694175266</v>
       </c>
-      <c r="E74" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" s="2">
         <v>608</v>
       </c>
@@ -5864,19 +5568,15 @@
         <v>75</v>
       </c>
       <c r="C75">
-        <f>((anual!I75-anual!D75)/7)/anual!D75</f>
-        <v>-2.9679669016130176E-3</v>
+        <f>(anual!J75-anual!C75)/(7*53-1)</f>
+        <v>-2.9246447753154703</v>
       </c>
       <c r="D75">
         <f>anual!C75</f>
         <v>36461.088623227894</v>
       </c>
-      <c r="E75" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" s="2">
         <v>609</v>
       </c>
@@ -5884,19 +5584,15 @@
         <v>76</v>
       </c>
       <c r="C76">
-        <f>((anual!I76-anual!D76)/7)/anual!D76</f>
-        <v>9.579872634006479E-3</v>
+        <f>(anual!J76-anual!C76)/(7*53-1)</f>
+        <v>5.3610473153385687</v>
       </c>
       <c r="D76">
         <f>anual!C76</f>
         <v>20834.340359595444</v>
       </c>
-      <c r="E76" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77" s="2">
         <v>610</v>
       </c>
@@ -5904,19 +5600,15 @@
         <v>77</v>
       </c>
       <c r="C77">
-        <f>((anual!I77-anual!D77)/7)/anual!D77</f>
-        <v>3.1887544107189175E-3</v>
+        <f>(anual!J77-anual!C77)/(7*53-1)</f>
+        <v>4.4117030962260806</v>
       </c>
       <c r="D77">
         <f>anual!C77</f>
         <v>51926.454889730572</v>
       </c>
-      <c r="E77" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" s="2">
         <v>611</v>
       </c>
@@ -5924,19 +5616,15 @@
         <v>78</v>
       </c>
       <c r="C78">
-        <f>((anual!I78-anual!D78)/7)/anual!D78</f>
-        <v>1.5777518215040986E-2</v>
+        <f>(anual!J78-anual!C78)/(7*53-1)</f>
+        <v>10.863631694767713</v>
       </c>
       <c r="D78">
         <f>anual!C78</f>
         <v>25410.003899916341</v>
       </c>
-      <c r="E78" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" s="2">
         <v>612</v>
       </c>
@@ -5944,19 +5632,15 @@
         <v>79</v>
       </c>
       <c r="C79">
-        <f>((anual!I79-anual!D79)/7)/anual!D79</f>
-        <v>2.8334736141647069E-3</v>
+        <f>(anual!J79-anual!C79)/(7*53-1)</f>
+        <v>0.36429583411924327</v>
       </c>
       <c r="D79">
         <f>anual!C79</f>
         <v>4723.7495104457066</v>
       </c>
-      <c r="E79" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80" s="2">
         <v>613</v>
       </c>
@@ -5964,19 +5648,15 @@
         <v>80</v>
       </c>
       <c r="C80">
-        <f>((anual!I80-anual!D80)/7)/anual!D80</f>
-        <v>1.3670338421210378E-2</v>
+        <f>(anual!J80-anual!C80)/(7*53-1)</f>
+        <v>4.647093784647006</v>
       </c>
       <c r="D80">
         <f>anual!C80</f>
         <v>12532.241626081443</v>
       </c>
-      <c r="E80" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" s="2">
         <v>701</v>
       </c>
@@ -5984,19 +5664,15 @@
         <v>81</v>
       </c>
       <c r="C81">
-        <f>((anual!I81-anual!D81)/7)/anual!D81</f>
-        <v>-1.8325655232655121E-3</v>
+        <f>(anual!J81-anual!C81)/(7*53-1)</f>
+        <v>-4.4829922559170834</v>
       </c>
       <c r="D81">
         <f>anual!C81</f>
         <v>93441.203508879888</v>
       </c>
-      <c r="E81" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" s="2">
         <v>702</v>
       </c>
@@ -6004,19 +5680,15 @@
         <v>82</v>
       </c>
       <c r="C82">
-        <f>((anual!I82-anual!D82)/7)/anual!D82</f>
-        <v>5.6549233603908162E-3</v>
+        <f>(anual!J82-anual!C82)/(7*53-1)</f>
+        <v>22.512723306008706</v>
       </c>
       <c r="D82">
         <f>anual!C82</f>
         <v>148901.97962131642</v>
       </c>
-      <c r="E82" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83" s="2">
         <v>703</v>
       </c>
@@ -6024,19 +5696,15 @@
         <v>83</v>
       </c>
       <c r="C83">
-        <f>((anual!I83-anual!D83)/7)/anual!D83</f>
-        <v>5.3800249334947682E-4</v>
+        <f>(anual!J83-anual!C83)/(7*53-1)</f>
+        <v>0.60125362744269351</v>
       </c>
       <c r="D83">
         <f>anual!C83</f>
         <v>56935.574463207653</v>
       </c>
-      <c r="E83" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" s="2">
         <v>704</v>
       </c>
@@ -6044,19 +5712,15 @@
         <v>84</v>
       </c>
       <c r="C84">
-        <f>((anual!I84-anual!D84)/7)/anual!D84</f>
-        <v>8.837789248615344E-3</v>
+        <f>(anual!J84-anual!C84)/(7*53-1)</f>
+        <v>10.228062337003742</v>
       </c>
       <c r="D84">
         <f>anual!C84</f>
         <v>42872.750282955603</v>
       </c>
-      <c r="E84" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" s="2">
         <v>705</v>
       </c>
@@ -6064,19 +5728,15 @@
         <v>85</v>
       </c>
       <c r="C85">
-        <f>((anual!I85-anual!D85)/7)/anual!D85</f>
-        <v>3.5209375646829922E-3</v>
+        <f>(anual!J85-anual!C85)/(7*53-1)</f>
+        <v>4.1724862312357454</v>
       </c>
       <c r="D85">
         <f>anual!C85</f>
         <v>44129.391173650161</v>
       </c>
-      <c r="E85" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" s="3">
         <v>706</v>
       </c>
@@ -6084,16 +5744,12 @@
         <v>86</v>
       </c>
       <c r="C86">
-        <f>((anual!I86-anual!D86)/7)/anual!D86</f>
-        <v>7.7234079986302972E-3</v>
+        <f>(anual!J86-anual!C86)/(7*53-1)</f>
+        <v>11.465274173572107</v>
       </c>
       <c r="D86">
         <f>anual!C86</f>
         <v>55137.943035120479</v>
-      </c>
-      <c r="E86" s="4">
-        <f t="shared" si="1"/>
-        <v>9.4339622641509441E-2</v>
       </c>
     </row>
   </sheetData>
